--- a/لوجيستيات.xlsx
+++ b/لوجيستيات.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/karimmokhtar/المتوكل/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{509AA0E2-F488-3844-8367-39A8697F0548}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82C4962E-8ECA-FC4F-AE3E-69BB7BAD8C06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="600" windowWidth="28040" windowHeight="16180" xr2:uid="{45FD3EBF-C8E9-7544-81A0-D4403E950FB1}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="972" uniqueCount="547">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1772" uniqueCount="1030">
   <si>
     <t>اسم الشركة المحتملة</t>
   </si>
@@ -3617,13 +3617,2333 @@
   </si>
   <si>
     <t>م</t>
+  </si>
+  <si>
+    <t>شركة الأمل فورت للحاصلات الزراعية</t>
+  </si>
+  <si>
+    <t>شركة العلاقية لتصنيع وتعبئة الحاصلات</t>
+  </si>
+  <si>
+    <t>شركة بريمير للمصدرين (Premier Exporters)</t>
+  </si>
+  <si>
+    <t>شركة عبد الوهاب وأولاده للحاصلات</t>
+  </si>
+  <si>
+    <t>شركة فارم فريتس للاستثمار الزراعي</t>
+  </si>
+  <si>
+    <t>شركة البردي الدولية للحاصلات</t>
+  </si>
+  <si>
+    <t>شركة مصر الدولية لتهيئة وتصدير الحاصلات</t>
+  </si>
+  <si>
+    <t>شركة النجار للتجارة الدولية للحاصلات</t>
+  </si>
+  <si>
+    <t>شركة دي ام اف لتصنيع وإعداد الحاصلات</t>
+  </si>
+  <si>
+    <t>شركة جالينا جروب للصناعات الزراعية</t>
+  </si>
+  <si>
+    <t>شركة أجرواكورب للحاصلات الزراعية</t>
+  </si>
+  <si>
+    <t>شركة سوناك الأهلية لتصدير الحاصلات</t>
+  </si>
+  <si>
+    <t>شركة أجرواأليكس لاستيراد وتصدير الحاصلات</t>
+  </si>
+  <si>
+    <t>شركة بلو سكايز إيجيبت للحاصلات</t>
+  </si>
+  <si>
+    <r>
+      <t>تعبئة وتصدير المحاصيل الزراعية والبقوليات (صادر)</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="7.2"/>
+        <color rgb="FF444746"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>13</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ميرسك (Maersk)</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="7.2"/>
+        <color rgb="FF444746"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>14</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>النجار للملاحة والنقل</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="7.2"/>
+        <color rgb="FF444746"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>15</t>
+    </r>
+  </si>
+  <si>
+    <t>البحيرة - دمنهور</t>
+  </si>
+  <si>
+    <t>أ. فتح الله محمد (مدير التصدير)</t>
+  </si>
+  <si>
+    <t>Alamal@Alamal.com</t>
+  </si>
+  <si>
+    <t>تجهيز وتعبئة وتصدير البقوليات واللب والسمسم (صادر/وارد)</t>
+  </si>
+  <si>
+    <t>البحيرة - حوش عيسى</t>
+  </si>
+  <si>
+    <t>أ. عامر العلاقية (المدير العام)</t>
+  </si>
+  <si>
+    <t>ALALLAKY3010@ALALLAKY.COM</t>
+  </si>
+  <si>
+    <t>تصدير الفواكه الجافة والطازجة والبقوليات والسمسم لأسواق أوروبا وآسيا (صادر)</t>
+  </si>
+  <si>
+    <t>الإسكندرية - رشدي</t>
+  </si>
+  <si>
+    <t>أ. محمود بدر (رئيس مجلس الإدارة)</t>
+  </si>
+  <si>
+    <t>sales@premierexporters.com</t>
+  </si>
+  <si>
+    <t>ترست للخدمات الملاحية</t>
+  </si>
+  <si>
+    <t>البحيرة - أبو المطامير</t>
+  </si>
+  <si>
+    <t>أ. عبير عزيز (مسئول العلاقات والتصدير)</t>
+  </si>
+  <si>
+    <t>abdelwahab.fruit@yahoo.com</t>
+  </si>
+  <si>
+    <t>المرجان للنقل الدولي</t>
+  </si>
+  <si>
+    <t>شركة أجرولاند للتصنيع الزراعي (Agroland)</t>
+  </si>
+  <si>
+    <t>زراعة وتعبئة وتصدير الموالح والبطاطس والبصل للأسواق العالمية (صادر)</t>
+  </si>
+  <si>
+    <t>الإسكندرية - الأزاريطة</t>
+  </si>
+  <si>
+    <t>أ. وائل النجار (نائب رئيس مجلس الإدارة)</t>
+  </si>
+  <si>
+    <t>info@agroland-eg.com</t>
+  </si>
+  <si>
+    <t>النجار للملاحة والنقل</t>
+  </si>
+  <si>
+    <t>تصنيع وتعبئة وتصدير الفواكه الطازجة والمجمدة والموالح (صادر)</t>
+  </si>
+  <si>
+    <t>أ. نهال محسن (مدير اللوجستيات)</t>
+  </si>
+  <si>
+    <t>logistics@farmfruits.com</t>
+  </si>
+  <si>
+    <t>كادمار للنقل والخدمات</t>
+  </si>
+  <si>
+    <t>شركة أجرواستار للزراعة الحديثة (Agrostar)</t>
+  </si>
+  <si>
+    <t>زراعة وتعبئة وتصدير الحمضيات والفواكه الطازجة لأوروبا وروسيا (صادر)</t>
+  </si>
+  <si>
+    <t>البحيرة - طريق مصر الصحراوي</t>
+  </si>
+  <si>
+    <t>أ. صلاح محمد (مدير التصدير)</t>
+  </si>
+  <si>
+    <t>info@agrostar-eg.com</t>
+  </si>
+  <si>
+    <t>شركة أجرين للاستثمار الزراعي (Agreen)</t>
+  </si>
+  <si>
+    <t>تصدير الموالح والفاكهة الطازجة وتعبئتها في محطات معتمدة (صادر)</t>
+  </si>
+  <si>
+    <t>أ. نهال محسن (مدير اللوجستيات والتحميل)</t>
+  </si>
+  <si>
+    <t>info@agreen-co.com</t>
+  </si>
+  <si>
+    <t>شركة البنا للحاصلات الزراعية (El Banna)</t>
+  </si>
+  <si>
+    <t>تعبئة وتصدير الموالح والعنب والبطاطس لأسواق أوروبا وروسيا (صادر)</t>
+  </si>
+  <si>
+    <t>أ. البنا (مدير التصدير واللوجستيات)</t>
+  </si>
+  <si>
+    <t>info@elbanna-eg.com</t>
+  </si>
+  <si>
+    <t>فرز وتصدير الجوافة والفواكه الطازجة والمجمدة والموالح (صادر)</t>
+  </si>
+  <si>
+    <t>أ. محمد البردي (مدير التصدير)</t>
+  </si>
+  <si>
+    <t>export@elbardyinternational.com</t>
+  </si>
+  <si>
+    <t>فرز وتعبئة وتصدير الفول والعدس والسمسم والترمس (صادر/وارد)</t>
+  </si>
+  <si>
+    <t>د. أنور هنيدي (مدير التسويق والتصدير)</t>
+  </si>
+  <si>
+    <t>Egypt_international_co@yahoo.com</t>
+  </si>
+  <si>
+    <t>ترست للتخليص والنقل</t>
+  </si>
+  <si>
+    <t>استيراد وتوزيع البقوليات والحبوب وتصدير المحاصيل الجافة (صادر/وارد)</t>
+  </si>
+  <si>
+    <t>الإسكندرية - المنشية</t>
+  </si>
+  <si>
+    <t>أ. تامر النجار (المدير التنفيذي للعمليات)</t>
+  </si>
+  <si>
+    <t>tamer@naggari.com</t>
+  </si>
+  <si>
+    <t>فرز وتعبئة وتصدير الفول السوداني والبقوليات والسمسم (صادر/وارد)</t>
+  </si>
+  <si>
+    <t>د. محمود فاروق محمود (المالك ومدير المبيعات)</t>
+  </si>
+  <si>
+    <t>dmfagroproducts@gmail.com</t>
+  </si>
+  <si>
+    <t>شركة أجروايجيبت لتصنيع وتعبئة المواد</t>
+  </si>
+  <si>
+    <t>تجفيف وتعبئة وتصدير البصل والبطاطس والفاكهة (صادر)</t>
+  </si>
+  <si>
+    <t>أ. محمد سالم شاهين (المدير العام للتصدير)</t>
+  </si>
+  <si>
+    <t>samerelkholy1@yahoo.com</t>
+  </si>
+  <si>
+    <t>شركة سيلفا للمنتجات الغذائية المجمدة الراقية</t>
+  </si>
+  <si>
+    <t>إنتاج وتصدير الفراولة والخضروات والفاكهة المجمدة (صادر)</t>
+  </si>
+  <si>
+    <t>أ. ميشيل عصام عدلي (نائب رئيس مجلس الإدارة)</t>
+  </si>
+  <si>
+    <t>michel.adly@silva-eg.com</t>
+  </si>
+  <si>
+    <t>تصنيع وتجميد وتصدير الخضروات والفواكه والمركزات لأوروبا (صادر)</t>
+  </si>
+  <si>
+    <t>م. محمد عبد الواحد سليمان (نائب رئيس مجلس الإدارة)</t>
+  </si>
+  <si>
+    <t>vice-president@galina-eg.com</t>
+  </si>
+  <si>
+    <t>تصدير الفاصوليا البيضاء والسمسم والترمس والبطاطس (صادر/وارد)</t>
+  </si>
+  <si>
+    <t>أ. عبد السميع فتحي (المدير المالي للتصدير)</t>
+  </si>
+  <si>
+    <t>sec@foodegypt.com</t>
+  </si>
+  <si>
+    <t>فرز وتعبئة وتصدير الموالح والبطاطس والبصل والرمان (صادر)</t>
+  </si>
+  <si>
+    <t>أ. عادل سوناك (مدير التصدير واللوجستيات)</t>
+  </si>
+  <si>
+    <t>export@sonac-eg.com</t>
+  </si>
+  <si>
+    <t>تعبئة وتصدير البطاطس والبرتقال والبصل والثوم لروسيا وأوروبا (صادر)</t>
+  </si>
+  <si>
+    <t>الإسكندرية - الشاطبي</t>
+  </si>
+  <si>
+    <t>أ. أحمد البسيوني (مدير العمليات والتطوير)</t>
+  </si>
+  <si>
+    <t>aelbessoumy@agroalexgroup.com</t>
+  </si>
+  <si>
+    <t>تجهيز وتعبئة وتصدير الفواكه الطازجة وسلطات الفواكه المقطعة (صادر)</t>
+  </si>
+  <si>
+    <t>الإسماعيلية - مدينة الإسماعيلية</t>
+  </si>
+  <si>
+    <t>أ. جون (مدير التصدير اللوجستي)</t>
+  </si>
+  <si>
+    <t>info@blueskiesegypt.com</t>
+  </si>
+  <si>
+    <r>
+      <t>فرز وتعبئة وتصدير الموالح والفواكه الطازجة (صادر)</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="7.2"/>
+        <color rgb="FF444746"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>17</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>البحيرة - حوش عيسى</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="7.2"/>
+        <color rgb="FF444746"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>18</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>المنوفية - مدينة السادات</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="7.2"/>
+        <color rgb="FF444746"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>19</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>كادمار للنقل والخدمات</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="7.2"/>
+        <color rgb="FF444746"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>16</t>
+    </r>
+  </si>
+  <si>
+    <t>شركة بسكو مصر (Bisco Misr)</t>
+  </si>
+  <si>
+    <t>تصنيع وتصدير البسكويت والمخبوزات الجافة (صادر/وارد)</t>
+  </si>
+  <si>
+    <t>شركة إيجيبت تريد للصناعات الغذائية</t>
+  </si>
+  <si>
+    <t>إنتاج وتصدير السناكس والمقرمشات والأغذية الجافة (صادر)</t>
+  </si>
+  <si>
+    <t>شركة هاي فود للصناعات الغذائية</t>
+  </si>
+  <si>
+    <t>أرامكس للخدمات اللوجستية</t>
+  </si>
+  <si>
+    <t>شركة ماس فود للصناعات الغذائية</t>
+  </si>
+  <si>
+    <t>إنتاج وتصدير حبوب الإفطار والمخبوزات (صادر/وارد)</t>
+  </si>
+  <si>
+    <t>أ. تامر البهائي (مدير العمليات والتصدير)</t>
+  </si>
+  <si>
+    <t>شركة ريو للصناعات الغذائية (Rio Foods)</t>
+  </si>
+  <si>
+    <t>تجهيز وتعبئة وحفظ البقوليات والمواد الجافة (صادر/وارد)</t>
+  </si>
+  <si>
+    <t>أ. عمر ناصر (مدير المبيعات والتصدير)</t>
+  </si>
+  <si>
+    <t>دي إتش إل سلاسل الإمداد (DHL)</t>
+  </si>
+  <si>
+    <t>الشركة الوطنية للصناعات الغذائية (الشماع)</t>
+  </si>
+  <si>
+    <t>إنتاج وتصدير المربيات والحلويات والصلصة (صادر/وارد)</t>
+  </si>
+  <si>
+    <t>أ. أحمد عبد الواحد (مدير التصدير واللوجستيات)</t>
+  </si>
+  <si>
+    <t>كوهين آند ناجل (Kuehne+Nagel)</t>
+  </si>
+  <si>
+    <t>شركة السنابل للاستيراد وتعبئة الأغذية</t>
+  </si>
+  <si>
+    <t>تعبئة وتصدير البقوليات والسمسم والأرز (صادر/وارد)</t>
+  </si>
+  <si>
+    <t>أ. أحمد محيي (مدير التصدير والتسويق الدولي)</t>
+  </si>
+  <si>
+    <t>شركة وهبة مصر للصناعات الغذائية</t>
+  </si>
+  <si>
+    <t>تعبئة وتصدير الحبوب والبقوليات والأغذية (صادر/وارد)</t>
+  </si>
+  <si>
+    <t>أ. مفضل (المدير العام للتصدير اللوجستي)</t>
+  </si>
+  <si>
+    <t>مرساة جروب للتجارة والنقل</t>
+  </si>
+  <si>
+    <t>شركة ميديترانيو للصناعات</t>
+  </si>
+  <si>
+    <t>أ. مروان (مدير التصدير واللوجستيات جمركياً)</t>
+  </si>
+  <si>
+    <t>شركة هيربا لضرب وتصنيع الأرز</t>
+  </si>
+  <si>
+    <t>أ. عمرو مرسي (مدير التصدير والتحميل)</t>
+  </si>
+  <si>
+    <t>شركة جيفكو لمطاحن وتصنيع الأرز (Gefco)</t>
+  </si>
+  <si>
+    <t>تجهيز وضرب وتعبئة وتصدير الأرز الأبيض الفاخر (صادر)</t>
+  </si>
+  <si>
+    <t>أ. السعيد محروس شادي (رئيس مجلس الإدارة)</t>
+  </si>
+  <si>
+    <t>شركة Amal Al Hadith for Rice Mills</t>
+  </si>
+  <si>
+    <t>ضرب وتجهيز وتصدير الأرز الأبيض الفاخر (صادر)</t>
+  </si>
+  <si>
+    <t>أ. مصطفى السلتيسي (المدير العام والتسويق)</t>
+  </si>
+  <si>
+    <t>المرجان للنقل والملاحة</t>
+  </si>
+  <si>
+    <t>شركة النور للتجارة والتوكيلات (El Nour Co.)</t>
+  </si>
+  <si>
+    <t>استيراد الحبوب وتعبئة وتصدير البقوليات (صادر/وارد)</t>
+  </si>
+  <si>
+    <t>أ. تامر الواصف (مسئول الاستيراد والتصدير)</t>
+  </si>
+  <si>
+    <t>كادمار للملاحة والنقل</t>
+  </si>
+  <si>
+    <t>شركة المتحدة لتصنيع وتعبئة الزيوت</t>
+  </si>
+  <si>
+    <t>تكرير وتعبئة وتصدير الزيوت والدهون النباتية (صادر/وارد)</t>
+  </si>
+  <si>
+    <t>أ. رولا العتيبي (مسئول التصدير المالي)</t>
+  </si>
+  <si>
+    <t>شركة عافية العالمية (صافولا مصر - Savola)</t>
+  </si>
+  <si>
+    <t>أ. محمد وحيد (مدير اللوجستيات والتصدير)</t>
+  </si>
+  <si>
+    <t>شركة الإخوة أويل تك للزيوت والمنظفات</t>
+  </si>
+  <si>
+    <t>إنتاج وتكرير وتصدير زيوت التزييت والدهون (صادر/وارد)</t>
+  </si>
+  <si>
+    <t>أ. مصطفى مرجان (مدير التصدير والعمليات)</t>
+  </si>
+  <si>
+    <t>شركة جالينا جروب (British Egyptian Co.)</t>
+  </si>
+  <si>
+    <t>تصنيع وتجميد وتصدير الفراولة والخضروات (صادر)</t>
+  </si>
+  <si>
+    <t>م. محمد عبد الواحد (نائب رئيس مجلس الإدارة)</t>
+  </si>
+  <si>
+    <t>شركة دهيدرو فودز (Dehydrofoods)</t>
+  </si>
+  <si>
+    <t>إنتاج وتجفيف وتصدير البصل والثوم والخضروات (صادر)</t>
+  </si>
+  <si>
+    <t>أ. رشا عبد الله محمد (العضو المنتدب للتصدير)</t>
+  </si>
+  <si>
+    <t>rasha.abdallah@olamnet.com</t>
+  </si>
+  <si>
+    <t>شركة آي كاب لتصنيع وتعبئة الأغذية</t>
+  </si>
+  <si>
+    <t>إنتاج وتجهيز وتصدير الخضروات المجمدة (صادر)</t>
+  </si>
+  <si>
+    <t>أ. وايل عادل (المدير المالي والتنفيذي للتصدير)</t>
+  </si>
+  <si>
+    <t>شركة هيلسي فودز مصر (Healthy Foods)</t>
+  </si>
+  <si>
+    <t>تصنيع وتعبئة وتصدير الخضروات والفاكهة (صادر)</t>
+  </si>
+  <si>
+    <t>بني سويف - بياض العرب</t>
+  </si>
+  <si>
+    <t>أ. خالد عماد راشد (المدير العام للتصدير)</t>
+  </si>
+  <si>
+    <t>factory@healthyfoodsegypt.com</t>
+  </si>
+  <si>
+    <r>
+      <t>إنتاج البسكويت والحلويات والشوكولاته وتصديرها (صادر/وارد)</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="7.2"/>
+        <color rgb="FF444746"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>تصدير البقوليات والسمسم واستيراد خامات الحبوب (صادر/وارد)</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="7.2"/>
+        <color rgb="FF444746"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ضرب وتعبئة وتصدير الأرز الفاخر دولياً (صادر)</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="7.2"/>
+        <color rgb="FF444746"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>تكرير وتعبئة وتصدير زيوت الطعام والسمن (صادر/وارد)</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="7.2"/>
+        <color rgb="FF444746"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>القاهرة - الأميرية</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="7.2"/>
+        <color rgb="FF444746"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>الجيزة - مدينة 6 أكتوبر</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="7.2"/>
+        <color rgb="FF444746"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>الشرقية - العاشر من رمضان</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="7.2"/>
+        <color rgb="FF444746"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>بني سويف - بني سويف الجديدة</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="7.2"/>
+        <color rgb="FF444746"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>القليوبية - مدينة العبور</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="7.2"/>
+        <color rgb="FF444746"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>القاهرة - المعادي الجديدة</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="7.2"/>
+        <color rgb="FF444746"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>القاهرة - مدينة العبور</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="7.2"/>
+        <color rgb="FF444746"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>القاهرة - القاهرة الجديدة</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="7.2"/>
+        <color rgb="FF444746"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>القاهرة - مصر الجديدة</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="7.2"/>
+        <color rgb="FF444746"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>الدقهلية - المنصورة</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="7.2"/>
+        <color rgb="FF444746"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>كفر الشيخ - فوه</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="7.2"/>
+        <color rgb="FF444746"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>الدقهلية - شربين</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="7.2"/>
+        <color rgb="FF444746"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>القاهرة - منطقة المصانع</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="7.2"/>
+        <color rgb="FF444746"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>المنوفية - مدينة السادات</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="7.2"/>
+        <color rgb="FF444746"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>الشرقية - العاشر من رمضان</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="7.2"/>
+        <color rgb="FF444746"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>أ. تامر النجار (مسؤول المشتريات والتصدير)</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="7.2"/>
+        <color rgb="FF444746"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>أ. هاني الغريب (المدير العام والتسويق)</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="7.2"/>
+        <color rgb="FF444746"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>أ. عمرو إيهاب (مدير التصدير واللوجستيات)</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="7.2"/>
+        <color rgb="FF444746"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Ahmed.Mokbel@kellogg.com</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="7.2"/>
+        <color rgb="FF444746"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>hany_jobs@yahoo.com</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="7.2"/>
+        <color rgb="FF444746"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>amr.ihab@pladisglobal.com</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="7.2"/>
+        <color rgb="FF444746"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>tamer@massfood.com</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="7.2"/>
+        <color rgb="FF444746"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>info@riofoodsegypt.com</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="7.2"/>
+        <color rgb="FF444746"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ahmed@elshammaa.com</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="7.2"/>
+        <color rgb="FF444746"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>elsanabel@elsanabel.org</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="7.2"/>
+        <color rgb="FF444746"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>me@mufaddal.com</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="7.2"/>
+        <color rgb="FF444746"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>marwan.elkholi@mediterraneo-egypt.com</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="7.2"/>
+        <color rgb="FF444746"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Amr.morsy@herbaricemills.com</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="7.2"/>
+        <color rgb="FF444746"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>info@gefcomills.com</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="7.2"/>
+        <color rgb="FF444746"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>elamal.mill@yahoo.com</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="7.2"/>
+        <color rgb="FF444746"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>m.a.elwaseef@gmail.com</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="7.2"/>
+        <color rgb="FF444746"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>r.alotaibi@unitedoil-eg.com</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="7.2"/>
+        <color rgb="FF444746"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>mohamed.wahid@savola.com</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="7.2"/>
+        <color rgb="FF444746"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>mustafa@oiltecegypt.com</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="7.2"/>
+        <color rgb="FF444746"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>wael.adel@icapp.com.eg</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="7.2"/>
+        <color rgb="FF444746"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>دي إتش إل سلاسل الإمداد (DHL)</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="7.2"/>
+        <color rgb="FF444746"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>21</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>كوهين آند ناجل (Kuehne+Nagel)</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="7.2"/>
+        <color rgb="FF444746"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>22</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>مرساة جروب للتجارة والنقل</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="7.2"/>
+        <color rgb="FF444746"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>23</t>
+    </r>
+  </si>
+  <si>
+    <t>الشركة المصرية للتجارة والصناعة (SOGIC)</t>
+  </si>
+  <si>
+    <t>تصنيع وتصدير المنسوجات والملابس الجاهزة (صادر/وارد)</t>
+  </si>
+  <si>
+    <t>إيكو وورلد وايد إيجيبت</t>
+  </si>
+  <si>
+    <t>مصنع ملابس قناة السويس (Suez Canal)</t>
+  </si>
+  <si>
+    <t>إنتاج وتصدير الملابس الجاهزة والقمصان (صادر)</t>
+  </si>
+  <si>
+    <t>أ. أشرف عبد الفتاح (مدير التسويق والتصدير)</t>
+  </si>
+  <si>
+    <t>mohamed-fawzy@scg.com.eg</t>
+  </si>
+  <si>
+    <t>ال مارين للخدمات اللوجستية</t>
+  </si>
+  <si>
+    <t>شركة نايل كلوذنج للملابس الجاهزة</t>
+  </si>
+  <si>
+    <t>تصنيع وتصدير البدلات والملابس الكاجوال (صادر/وارد)</t>
+  </si>
+  <si>
+    <t>أ. إبراهيم حيدر (مدير الاستيراد والتصدير)</t>
+  </si>
+  <si>
+    <t>ebrahim@nilecc.com</t>
+  </si>
+  <si>
+    <t>ترانسبورتر للشحن اللوجستي</t>
+  </si>
+  <si>
+    <t>شركة الملابس السويسرية (Swiss Garments)</t>
+  </si>
+  <si>
+    <t>إنتاج وتصدير الملابس الجاهزة والبدلات الكلاسيكية (صادر)</t>
+  </si>
+  <si>
+    <t>أ. علاء أحمد عرفة (رئيس مجلس الإدارة)</t>
+  </si>
+  <si>
+    <t>aarafa@sgc.com.eg</t>
+  </si>
+  <si>
+    <t>أراب إكسبريس للملاحة ونقل</t>
+  </si>
+  <si>
+    <t>شركة النيل للمنسوجات والملابس الجاهزة</t>
+  </si>
+  <si>
+    <t>صناعة وتجهيز وتصدير المنسوجات الجاهزة (صادر)</t>
+  </si>
+  <si>
+    <t>بورسعيد - المنطقة الحرة</t>
+  </si>
+  <si>
+    <t>أ. وليد علي محمد هريدي (مدير التصدير والاستيراد)</t>
+  </si>
+  <si>
+    <t>waleedhar@hotmail.com</t>
+  </si>
+  <si>
+    <t>الرحمة للنقل والشحن الدولي</t>
+  </si>
+  <si>
+    <t>شركة ترانس أفريكا لصناعة الملابس</t>
+  </si>
+  <si>
+    <t>إنتاج وتصدير الملابس الكاجوال والجينز لأوروبا (صادر)</t>
+  </si>
+  <si>
+    <t>أ. سمير فتح الله (المدير التنفيذي للتصدير)</t>
+  </si>
+  <si>
+    <t>samer@tafricagarments.com</t>
+  </si>
+  <si>
+    <t>شركة الشرق الأوسط للمنسوجات (METECO)</t>
+  </si>
+  <si>
+    <t>إنتاج وتصدير الأقمشة والملابس الجاهزة (صادر/وارد)</t>
+  </si>
+  <si>
+    <t>بورسعيد - جلف لاند</t>
+  </si>
+  <si>
+    <t>أ. شريف أحمد مردان (المدير العام للتصدير)</t>
+  </si>
+  <si>
+    <t>sherifm@metco-eg.com</t>
+  </si>
+  <si>
+    <t>شركة مارتكس فاشون للملابس</t>
+  </si>
+  <si>
+    <t>تصنيع وتصدير الملابس الجاهزة والتريكو (صادر)</t>
+  </si>
+  <si>
+    <t>القليوبية - الخانكة</t>
+  </si>
+  <si>
+    <t>أ. حسين حسين دسوقي (مسئول التصدير والتواصل)</t>
+  </si>
+  <si>
+    <t>hussein.dsouky@gmail.com</t>
+  </si>
+  <si>
+    <t>شركة نيو ناجح تكس للمنسوجات الحديثة</t>
+  </si>
+  <si>
+    <t>تصنيع خيوط الغزل وصباغة الأقمشة الدائرية (صادر)</t>
+  </si>
+  <si>
+    <t>أ. فيكتور صبري عزيز (مشرف التجارة الخارجية)</t>
+  </si>
+  <si>
+    <t>INFO@Nagehtex.com</t>
+  </si>
+  <si>
+    <t>شركة رويال للصناعات النسيجية</t>
+  </si>
+  <si>
+    <t>تصنيع وتعبئة وتصدير الملابس الجاهزة والمنسوجات (صادر)</t>
+  </si>
+  <si>
+    <t>أ. أحمد محمد عبدو (المدير العام للتصدير والجمارك)</t>
+  </si>
+  <si>
+    <t>ahmedabdou@globalnet.com</t>
+  </si>
+  <si>
+    <t>شركة الفان لغزل ونسيج وصباغة الأقمشة</t>
+  </si>
+  <si>
+    <t>إنتاج وتجهيز وصباغة وتصدير المنسوجات الدائرية (صادر/وارد)</t>
+  </si>
+  <si>
+    <t>أ. رضا أبو العينين (مدير التصدير والاستيراد)</t>
+  </si>
+  <si>
+    <t>exporting@RubyredGarment.com</t>
+  </si>
+  <si>
+    <t>شركة نيو ستار لتصنيع وتصدير الملابس</t>
+  </si>
+  <si>
+    <t>إنتاج وتعبئة وتصدير الملابس الجاهزة والجينز (صادر)</t>
+  </si>
+  <si>
+    <t>أ. معتز محمود حسن (مدير التصدير جمركياً)</t>
+  </si>
+  <si>
+    <t>motaz_srror@yahoo.com</t>
+  </si>
+  <si>
+    <t>شركة موسى كاب لتصنيع المنسوجات</t>
+  </si>
+  <si>
+    <t>تصنيع وتصدير القبعات والملابس الجاهزة (صادر/وارد)</t>
+  </si>
+  <si>
+    <t>الإسكندرية - المنتزة</t>
+  </si>
+  <si>
+    <t>أ. عمر إبراهيم أحمد (المدير المالي للتصدير)</t>
+  </si>
+  <si>
+    <t>accomar15778@yahoo.com</t>
+  </si>
+  <si>
+    <t>شركة الدقهلية للغزل والنسيج</t>
+  </si>
+  <si>
+    <t>غزل ونسيج وصباغة وتجهيز الأقمشة والمنسوجات (صادر/وارد)</t>
+  </si>
+  <si>
+    <t>الدقهلية - المنصورة</t>
+  </si>
+  <si>
+    <t>أ. علياء علي الزهيري (المدير العام للتصدير والعمليات)</t>
+  </si>
+  <si>
+    <t>detex_22@yahoo.com</t>
+  </si>
+  <si>
+    <t>شركة ميجا تيكستايل للغزل والنسيج</t>
+  </si>
+  <si>
+    <t>تصنيع خيوط الغزل وصباغة الأقمشة القطنية (صادر)</t>
+  </si>
+  <si>
+    <t>أ. محمد بدري (مدير التجارة الخارجية والتصدير)</t>
+  </si>
+  <si>
+    <t>akyardlly@megaiv.com</t>
+  </si>
+  <si>
+    <t>شركة كيميت فاشون للملابس الجاهزة</t>
+  </si>
+  <si>
+    <t>إنتاج وتصدير البدلات والقمصان والملابس الجاهزة (صادر)</t>
+  </si>
+  <si>
+    <t>أ. عادل محمد السعيد (المدير العام للتصدير)</t>
+  </si>
+  <si>
+    <t>kemet_fashion@hotmail.com</t>
+  </si>
+  <si>
+    <t>شركة دايس للملابس الرياضية والكاجوال</t>
+  </si>
+  <si>
+    <t>تصنيع وتصدير الملابس الرياضية والجاهزة لأسواق أمريكا (صادر)</t>
+  </si>
+  <si>
+    <t>أ. ناجي سمير توما (المدير التنفيذي للتصدير)</t>
+  </si>
+  <si>
+    <t>george@dicefactory.net</t>
+  </si>
+  <si>
+    <t>شركة وايلتكس لصباغة وتصنيع الملابس</t>
+  </si>
+  <si>
+    <t>صباغة وتجهيز الأقمشة وتصدير الملابس الكاجوال (صادر/وارد)</t>
+  </si>
+  <si>
+    <t>الإسكندرية - باكوس</t>
+  </si>
+  <si>
+    <t>أ. ريمون وديع إبراهيم (مدير التصدير واللوجستيات)</t>
+  </si>
+  <si>
+    <t>waeltex@link.net</t>
+  </si>
+  <si>
+    <t>شركة يسرى لإنتاج التريكو والملابس</t>
+  </si>
+  <si>
+    <t>إنتاج وتعبئة وتصدير ملابس التريكو للولايات المتحدة (صادر)</t>
+  </si>
+  <si>
+    <t>الإسكندرية - النزهة</t>
+  </si>
+  <si>
+    <t>أ. يسري محمد سليمان (المالك والمدير العام للتصدير)</t>
+  </si>
+  <si>
+    <t>trico_yousri@yahoo.com</t>
+  </si>
+  <si>
+    <t>شركة لوتس لإنتاج وتصدير الملابس</t>
+  </si>
+  <si>
+    <t>تصنيع وتصدير الجينز والملابس الكاجوال لأمريكا (صادر)</t>
+  </si>
+  <si>
+    <t>أ. ممدوح سعد النبوي (مدير التخطيط والتصدير اللوجستي)</t>
+  </si>
+  <si>
+    <t>m.saad@lotus-garments.com.eg</t>
+  </si>
+  <si>
+    <r>
+      <t>الإسكندرية - محرم بك</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="7.2"/>
+        <color rgb="FF444746"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>25</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>بورسعيد - المنطقة الحرة</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="7.2"/>
+        <color rgb="FF444746"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>28</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>الجيزة - البدرشين</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="7.2"/>
+        <color rgb="FF444746"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>24</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>الإسكندرية - المنطقة الحرة بالعامرية</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="7.2"/>
+        <color rgb="FF444746"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>29</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>بورسعيد - المنطقة الحرة</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="7.2"/>
+        <color rgb="FF444746"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>أ. علي حسين (مدير الاستيراد والتصدير)</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="7.2"/>
+        <color rgb="FF444746"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>26</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>sogic@link.net</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="7.2"/>
+        <color rgb="FF444746"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>27</t>
+    </r>
+  </si>
+  <si>
+    <t>شركة سيدي كرير للبتروكيماويات (سيدبك)</t>
+  </si>
+  <si>
+    <t>م. أحمد علي (مسؤول التصدير جمركياً)</t>
+  </si>
+  <si>
+    <t>export@sidpec.com</t>
+  </si>
+  <si>
+    <t>وكالة الخليج (مصر) - GAC</t>
+  </si>
+  <si>
+    <t>الشركة المصرية لإنتاج الإيثيلين (إيثيدكو)</t>
+  </si>
+  <si>
+    <t>إنتاج وتصدير البولي إيثيلين منخفض الكثافة (صادر/وارد)</t>
+  </si>
+  <si>
+    <t>أ. سعد محمود (مدير اللوجستيات والتصدير)</t>
+  </si>
+  <si>
+    <t>export@ethydco-eg.com</t>
+  </si>
+  <si>
+    <t>الرشد لخدمات الشحن واللوجستيات</t>
+  </si>
+  <si>
+    <t>شركة إي يو بي مصر للكيماويات (EuP Egypt)</t>
+  </si>
+  <si>
+    <t>إنتاج الكيماويات المتخصصة ومضافات البلاستيك (صادر)</t>
+  </si>
+  <si>
+    <t>م. محمود منير سليمان (مدير العمليات والتصدير)</t>
+  </si>
+  <si>
+    <t>info@eupegypt.com</t>
+  </si>
+  <si>
+    <t>أبو هاشم للتخزين والنقل الجمركي</t>
+  </si>
+  <si>
+    <t>شركة الزين لصناعة وتجارة الكيماويات</t>
+  </si>
+  <si>
+    <t>تصنيع الراتنجات والمواد اللاصقة الكيميائية (صادر/وارد)</t>
+  </si>
+  <si>
+    <t>أ. أحمد الزين (المدير العام للتصدير والعمليات)</t>
+  </si>
+  <si>
+    <t>info@elzainchem.com</t>
+  </si>
+  <si>
+    <t>شركة دونسيري للبوليستر ومواد التغليف</t>
+  </si>
+  <si>
+    <t>إنتاج وتصدير رقائق وخامات البوليستر والبوليمرات (صادر/وارد)</t>
+  </si>
+  <si>
+    <t>السويس - السويس الجديدة</t>
+  </si>
+  <si>
+    <t>أ. عمرو فايد (المدير العام للتصدير والعلاقات)</t>
+  </si>
+  <si>
+    <t>amr.fayed@eg.ivldhunseri.com</t>
+  </si>
+  <si>
+    <t>شركة إندوراما فينشرز مصر للبتروكيماويات</t>
+  </si>
+  <si>
+    <t>إنتاج وتصدير البولي إيثيلين تيريفثاليت الغذائي (صادر/وارد)</t>
+  </si>
+  <si>
+    <t>أ. خالد سمير (مدير التصدير واللوجستيات جمركياً)</t>
+  </si>
+  <si>
+    <t>info@indorama-eg.com</t>
+  </si>
+  <si>
+    <t>شركة إيفكو مصر لتصنيع الزيوت والدهون</t>
+  </si>
+  <si>
+    <t>تصنيع وتكرير وتصدير الزيوت والدهون الكيميائية (صادر/وارد)</t>
+  </si>
+  <si>
+    <t>أ. محمد وحيد (مدير التصدير والشحن الدولي)</t>
+  </si>
+  <si>
+    <t>mohamed.wahid@iffco.com</t>
+  </si>
+  <si>
+    <t>شركة البتروكيماويات المصرية بالعامرية</t>
+  </si>
+  <si>
+    <t>م. سمير عبد الهادي (مدير التصدير جمركياً)</t>
+  </si>
+  <si>
+    <t>info@egyptianpetrochemicals.com</t>
+  </si>
+  <si>
+    <t>مصنع دهب لإنتاج وتعبئة المنظفات</t>
+  </si>
+  <si>
+    <t>إنتاج وتصدير المنظفات وتعبئة مساحيق الغسيل (صادر/وارد)</t>
+  </si>
+  <si>
+    <t>أ. خالد دهب (المدير العام للتشغيل والتصدير)</t>
+  </si>
+  <si>
+    <t>info@dahabdetergents.com</t>
+  </si>
+  <si>
+    <t>شركة البراق للاستثمار الصناعي والمنظفات</t>
+  </si>
+  <si>
+    <t>صناعة وتصدير المنظفات والصابون السائل للأواني (صادر/وارد)</t>
+  </si>
+  <si>
+    <t>أ. محمد البراق (مدير التصدير واللوجستيات)</t>
+  </si>
+  <si>
+    <t>info@alburagdetergents.com</t>
+  </si>
+  <si>
+    <t>شركة الجمال لصناعة الصابون والكيماويات</t>
+  </si>
+  <si>
+    <t>إنتاج وتصدير صابون التواليت والصابون الطبي (صادر/وارد)</t>
+  </si>
+  <si>
+    <t>أ. جمال محمد (المالك والمدير الفني للتصدير)</t>
+  </si>
+  <si>
+    <t>info@algamalsoap.com</t>
+  </si>
+  <si>
+    <t>شركة رويال هوم ايجيبت لإنتاج المنظفات</t>
+  </si>
+  <si>
+    <t>إنتاج وتصدير المنظفات الصناعية ومطهرات الأرضيات (صادر/وارد)</t>
+  </si>
+  <si>
+    <t>أ. ياسر الرويال (مدير التصدير والجمارك)</t>
+  </si>
+  <si>
+    <t>info@royalhomeegypt.com</t>
+  </si>
+  <si>
+    <t>شركة ايجيبت لإنتاج حمض التانيك والفلافونيدات</t>
+  </si>
+  <si>
+    <t>أ. شاهين أحمد (مدير التصدير والتحميل)</t>
+  </si>
+  <si>
+    <t>info@tanic-egypt.com</t>
+  </si>
+  <si>
+    <t>الشركة المصرية لخدمات الغاز والبترول</t>
+  </si>
+  <si>
+    <t>م. غازي كامل (المدير العام للتصدير والمبيعات)</t>
+  </si>
+  <si>
+    <t>info@egyptiangas-services.com</t>
+  </si>
+  <si>
+    <t>شركة ازكو للخدمات البترولية بالمنطقة الحرة</t>
+  </si>
+  <si>
+    <t>م. أزهري سليمان (مدير العمليات والتصدير)</t>
+  </si>
+  <si>
+    <t>info@azco-services.com</t>
+  </si>
+  <si>
+    <t>شركة الزيتون لإنتاج الكيماويات المتخصصة</t>
+  </si>
+  <si>
+    <t>إنتاج وتصدير المنظفات الكيماوية والمنظفات الصناعية (صادر)</t>
+  </si>
+  <si>
+    <t>أ. أحمد زيتون (مدير المبيعات والتصدير الدولي)</t>
+  </si>
+  <si>
+    <t>info@olive-chemicals.com</t>
+  </si>
+  <si>
+    <t>شركة تى دابليو ام ايه مصر لخدمات البترول</t>
+  </si>
+  <si>
+    <t>م. توفيق محمود (مدير التصدير جمركياً)</t>
+  </si>
+  <si>
+    <t>info@twma-egypt.com</t>
+  </si>
+  <si>
+    <t>شركة ميتكو للخدمات الملاحية والتصديرية (الملح)</t>
+  </si>
+  <si>
+    <t>استخراج وفرز وتعبئة وتصدير ملح الملاحات الصناعي (صادر)</t>
+  </si>
+  <si>
+    <t>أ. أحمد الجباس (مدير العمليات والتصدير اللوجستي)</t>
+  </si>
+  <si>
+    <t>info@mitco-egypt.com</t>
+  </si>
+  <si>
+    <t>شركة النصر للأسمدة والصناعات الكيماوية</t>
+  </si>
+  <si>
+    <t>تصنيع وتصدير كبريتات ونترات الأمونيوم والأسمدة (صادر)</t>
+  </si>
+  <si>
+    <t>أ. نصري حسني (مدير التصدير والتسويق الدولي)</t>
+  </si>
+  <si>
+    <t>info@nasr-fertilizers.com</t>
+  </si>
+  <si>
+    <r>
+      <t>إنتاج وتصدير البولي إيثيلين وغاز البوتاجاز والكلور (صادر/وارد)</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="7.2"/>
+        <color rgb="FF444746"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>إنتاج وتصدير الصودا الكاوية، غاز الكلور، والـ PVC (صادر/وارد)</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="7.2"/>
+        <color rgb="FF444746"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>33</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>استخلاص وإنتاج حمض التانيك والبوليفينول الطبيعي (صادر)</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="7.2"/>
+        <color rgb="FF444746"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>6</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>تقديم الخدمات الفنية وتداول وإمداد الغاز (وارد)</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="7.2"/>
+        <color rgb="FF444746"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>7</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>تقديم خدمات الدعم وحفر وتجهيز آبار النفط (وارد)</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="7.2"/>
+        <color rgb="FF444746"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>7</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>معالجة وإدارة مخلفات الحفر والحلول البيئية النفطية (وارد)</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="7.2"/>
+        <color rgb="FF444746"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>7</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>المنوفية - مدينة السادات</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="7.2"/>
+        <color rgb="FF444746"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>6</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>الإسكندرية - المنطقة الحرة بالعامرية</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="7.2"/>
+        <color rgb="FF444746"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>7</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ميرسك (Maersk)</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="7.2"/>
+        <color rgb="FF444746"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>31</t>
+    </r>
+  </si>
+  <si>
+    <t>الشركة المصرية للأسمدة والصناعات الكيماوية</t>
+  </si>
+  <si>
+    <t>إنتاج وتصدير الأسمدة الفوسفاتية وحامض النيتريك (صادر)</t>
+  </si>
+  <si>
+    <t>الدقهلية - طلخا</t>
+  </si>
+  <si>
+    <t>م. كيميائي أحمد (مدير التصدير واللوجستيات)</t>
+  </si>
+  <si>
+    <t>info@egyptian-fertilizers.com</t>
+  </si>
+  <si>
+    <t>شركة صناعة وسائل النقل (MCV)</t>
+  </si>
+  <si>
+    <t>تصنيع وتصدير الحافلات السياحية والشاحنات (صادر/وارد)</t>
+  </si>
+  <si>
+    <t>الشرقية - الصالحية الجديدة</t>
+  </si>
+  <si>
+    <t>أ. رامي عبد العزيز (مسئول التصدير واللوجستيات)</t>
+  </si>
+  <si>
+    <t>export@mcv-eg.com</t>
+  </si>
+  <si>
+    <t>فيرست سيتي للنقل والملاحة</t>
+  </si>
+  <si>
+    <t>شركة بروميتيون للإطارات المطاطية</t>
+  </si>
+  <si>
+    <t>تصنيع وتصدير إطارات النقل الثقيل والشاحنات (صادر/وارد)</t>
+  </si>
+  <si>
+    <t>م. بروميتيون (مدير اللوجستيات والتصدير جمركياً)</t>
+  </si>
+  <si>
+    <t>export@prometeon.com.eg</t>
+  </si>
+  <si>
+    <t>بي &amp; جي للخدمات الملاحية</t>
+  </si>
+  <si>
+    <t>شركة مصر للألومنيوم بنجع حمادي</t>
+  </si>
+  <si>
+    <t>تصنيع وتشكيل وتصدير قطاعات وقضبان الألومنيوم (صادر/وارد)</t>
+  </si>
+  <si>
+    <t>قنا - نجع حمادي</t>
+  </si>
+  <si>
+    <t>م. ألومنيوم أحمد (مدير المبيعات والتصدير الدولي)</t>
+  </si>
+  <si>
+    <t>export@egyptaluminum.com</t>
+  </si>
+  <si>
+    <t>مختار جروب للملاحة والنقل</t>
+  </si>
+  <si>
+    <t>الشركة الكندية العالمية للألومنيوم والزجاج</t>
+  </si>
+  <si>
+    <t>إنتاج قطاعات الألومنيوم المعمارية والواجهات (صادر/وارد)</t>
+  </si>
+  <si>
+    <t>أ. كندي (المدير العام للتصدير والعلاقات)</t>
+  </si>
+  <si>
+    <t>info@canadian-aluminum.com</t>
+  </si>
+  <si>
+    <t>الطائى للنقل والأعمال الملاحية</t>
+  </si>
+  <si>
+    <t>الشركة المتحدة للمسابك وتشكيل المعادن</t>
+  </si>
+  <si>
+    <t>إنتاج وتشكيل كرات طحن المعادن والمسبوكات (صادر/وارد)</t>
+  </si>
+  <si>
+    <t>أ. مسعد (مدير التصدير واللوجستيات والشحن)</t>
+  </si>
+  <si>
+    <t>info@united-foundries.com</t>
+  </si>
+  <si>
+    <t>دياموند للنقل والخدمات اللوجستية</t>
+  </si>
+  <si>
+    <t>شركة لورد إنترناشيونال لوسائل الحلاقة</t>
+  </si>
+  <si>
+    <t>تصنيع شفرات الحلاقة الدقيقة والماكينات وتصديرها (صادر/وارد)</t>
+  </si>
+  <si>
+    <t>أ. لورد (مدير اللوجستيات والتصدير والجمارك)</t>
+  </si>
+  <si>
+    <t>export@lord-international.com.eg</t>
+  </si>
+  <si>
+    <t>الشركة المصرية للسبائك الحديدية بإدفو</t>
+  </si>
+  <si>
+    <t>إنتاج وتصدير سبائك الفيروسيليكون للحديد والصلب (صادر)</t>
+  </si>
+  <si>
+    <t>أسوان - إدفو</t>
+  </si>
+  <si>
+    <t>م. سبائك (مدير التصدير والشحن الدولي جمركياً)</t>
+  </si>
+  <si>
+    <t>export@egyptian-alloys.com</t>
+  </si>
+  <si>
+    <t>شركة بروجريس للرخام والجرانيت للتصدير</t>
+  </si>
+  <si>
+    <t>تصنيع وتصدير ألواح وبلاط الرخام المصري الممتاز (صادر)</t>
+  </si>
+  <si>
+    <t>القاهرة - شق الثعبان</t>
+  </si>
+  <si>
+    <t>أ. عزيز بشرى (رئيس مجلس الإدارة للتصدير)</t>
+  </si>
+  <si>
+    <t>info@progressmarble-eg.com</t>
+  </si>
+  <si>
+    <t>شركة تاس فلورانس للرخام والمعادن والتعدين</t>
+  </si>
+  <si>
+    <t>استخراج وتصدير الرخام وخامات الفوسفات والكوارتز (صادر)</t>
+  </si>
+  <si>
+    <t>أ. أحمد عبد العال (المدير العام للتصدير اللوجستي)</t>
+  </si>
+  <si>
+    <t>a.abdelal@tasflowrance.com</t>
+  </si>
+  <si>
+    <t>شركة تاجر البناء الحديث للمعدات (MBM)</t>
+  </si>
+  <si>
+    <t>استيراد معدات البناء الثقيلة ورافعات المنصات (وارد)</t>
+  </si>
+  <si>
+    <t>الجيزة - طريق الإسكندرية الصحراوي</t>
+  </si>
+  <si>
+    <t>أ. عبد السلام حماد (المدير العام للتوريدات والجمارك)</t>
+  </si>
+  <si>
+    <t>mbm@mbmegypt.com</t>
+  </si>
+  <si>
+    <t>شركة إكستريم لمنتجات البى فى سى بالعامرية</t>
+  </si>
+  <si>
+    <t>تصنيع الأبواب والشبابيك من مادة الـ PVC للمقاولات (وارد)</t>
+  </si>
+  <si>
+    <t>أ. إكستريم (مدير التصدير والعمليات الدولية)</t>
+  </si>
+  <si>
+    <t>info@extreme-pvc.com</t>
+  </si>
+  <si>
+    <t>شركة إليكس ستيل للحديد والصناعات الهندسية</t>
+  </si>
+  <si>
+    <t>خراطة وتشكيل وتصنيع هياكل الحديد والصلب (وارد)</t>
+  </si>
+  <si>
+    <t>أ. ستيل (مدير اللوجستيات والتصدير والجمارك)</t>
+  </si>
+  <si>
+    <t>info@alex-steel.com</t>
+  </si>
+  <si>
+    <t>شركة الأقصى للألوميتال والديكور بالعامرية</t>
+  </si>
+  <si>
+    <t>تصنيع الأبواب والنوافذ والواجهات من الألومنيوم (وارد)</t>
+  </si>
+  <si>
+    <t>أ. أقصى (المدير العام للتصدير اللوجستي والجمارك)</t>
+  </si>
+  <si>
+    <t>info@alaqsa-alumetal.com</t>
+  </si>
+  <si>
+    <t>المصنع الهندسى للأعمال الميكانيكية بالعامرية</t>
+  </si>
+  <si>
+    <t>تصنيع قطع غيار ماكينات مصانع الحديد والصلب (وارد)</t>
+  </si>
+  <si>
+    <t>م. ميكانيكي (مدير التصدير والمبيعات الخارجية)</t>
+  </si>
+  <si>
+    <t>info@engineering-mechanical.com</t>
+  </si>
+  <si>
+    <t>شركة نيو هايتك للمستلزمات الصناعية</t>
+  </si>
+  <si>
+    <t>توريد وتصدير أنظمة الهواء المضغوط الهيدروليكية (صادر)</t>
+  </si>
+  <si>
+    <t>القاهرة - دار السلام</t>
+  </si>
+  <si>
+    <t>أ. جلال السمان (المدير العام للتصدير اللوجستي)</t>
+  </si>
+  <si>
+    <t>g.saman@newhitec-eg.com</t>
+  </si>
+  <si>
+    <t>شركة إنسول للحلول الهندسية المتكاملة</t>
+  </si>
+  <si>
+    <t>توفير الحلول الهندسية الكهربائية للمنشآت (صادر)</t>
+  </si>
+  <si>
+    <t>القاهرة - المعادي</t>
+  </si>
+  <si>
+    <t>أ. إنسول (مدير التصدير والعمليات اللوجستية)</t>
+  </si>
+  <si>
+    <t>info@insol-engineering.com</t>
+  </si>
+  <si>
+    <t>شركة لابتك مصر للتجهيزات الطبية والمعملية</t>
+  </si>
+  <si>
+    <t>تجهيز وتوريد مستلزمات المعامل الطبية والمختبرات (صادر/وارد)</t>
+  </si>
+  <si>
+    <t>الجيزة - المهندسين</t>
+  </si>
+  <si>
+    <t>د. إيهاب أديب (رئيس مجلس الإدارة للتصدير)</t>
+  </si>
+  <si>
+    <t>ehab.adib@labtec-egypt.com</t>
+  </si>
+  <si>
+    <t>شركة روك للتجارة والمستلزمات الأمنية</t>
+  </si>
+  <si>
+    <t>توريد وتصدير الخزائن الحديدية والحلول الأمنية (صادر)</t>
+  </si>
+  <si>
+    <t>القاهرة - وسط البلد</t>
+  </si>
+  <si>
+    <t>أ. نصيف (المدير العام للتصدير والعمليات الفنية)</t>
+  </si>
+  <si>
+    <t>nassif@rocktrade-eg.com</t>
+  </si>
+  <si>
+    <t>شركة الجونة للفنون وتصنيع الأثاث</t>
+  </si>
+  <si>
+    <t>تصميم وتصنيع وتصدير الأثاث المكتبي الراقي (صادر)</t>
+  </si>
+  <si>
+    <t>م. شريف أبو زيد (المدير العام للتصدير واللوجستيات)</t>
+  </si>
+  <si>
+    <t>s.zeid@elgorna.com</t>
+  </si>
+  <si>
+    <t>شركة أسعد للصلب وتشكيل المعادن بالعامرية</t>
+  </si>
+  <si>
+    <t>أ. أسعد (المدير العام للتصدير والتحميل واللوجستيات)</t>
+  </si>
+  <si>
+    <t>info@asaadsteel-eg.com</t>
+  </si>
+  <si>
+    <r>
+      <t>تشكيل المعادن وقص وتجارة ألواح الصلب الإنشائي (وارد)</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="7.2"/>
+        <color rgb="FF444746"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>7</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>الإسكندرية - العامرية</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="7.2"/>
+        <color rgb="FF444746"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>7</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -3654,8 +5974,16 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <vertAlign val="superscript"/>
+      <sz val="7.2"/>
+      <color rgb="FF444746"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3665,6 +5993,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF8FAFD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3747,7 +6087,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="2"/>
@@ -3789,11 +6129,209 @@
     <xf numFmtId="1" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" readingOrder="2"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" readingOrder="2"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="15">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF8FAFD"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="2"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="medium">
+          <color rgb="FFC4C7C5"/>
+        </right>
+        <top/>
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF8FAFD"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="2"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="medium">
+          <color rgb="FFC4C7C5"/>
+        </right>
+        <top/>
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF8FAFD"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="2"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="medium">
+          <color rgb="FFC4C7C5"/>
+        </right>
+        <top/>
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF8FAFD"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="2"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="medium">
+          <color rgb="FFC4C7C5"/>
+        </right>
+        <top/>
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF8FAFD"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="2"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="medium">
+          <color rgb="FFC4C7C5"/>
+        </right>
+        <top/>
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -3854,6 +6392,16 @@
         </patternFill>
       </fill>
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="2"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="medium">
+          <color rgb="FFC4C7C5"/>
+        </right>
+        <top/>
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -3985,216 +6533,6 @@
       </fill>
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="2"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="medium">
-          <color rgb="FFC4C7C5"/>
-        </right>
-        <top/>
-        <bottom style="medium">
-          <color rgb="FFC4C7C5"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF8FAFD"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="2"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="medium">
-          <color rgb="FFC4C7C5"/>
-        </right>
-        <top/>
-        <bottom style="medium">
-          <color rgb="FFC4C7C5"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF8FAFD"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="2"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="medium">
-          <color rgb="FFC4C7C5"/>
-        </right>
-        <top/>
-        <bottom style="medium">
-          <color rgb="FFC4C7C5"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF8FAFD"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="2"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="medium">
-          <color rgb="FFC4C7C5"/>
-        </right>
-        <top/>
-        <bottom style="medium">
-          <color rgb="FFC4C7C5"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF8FAFD"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="2"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="medium">
-          <color rgb="FFC4C7C5"/>
-        </right>
-        <top/>
-        <bottom style="medium">
-          <color rgb="FFC4C7C5"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF8FAFD"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="2"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="medium">
-          <color rgb="FFC4C7C5"/>
-        </right>
-        <top/>
-        <bottom style="medium">
-          <color rgb="FFC4C7C5"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF8FAFD"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="2"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="medium">
           <color rgb="FFC4C7C5"/>
         </left>
@@ -4203,41 +6541,6 @@
         <bottom style="medium">
           <color rgb="FFC4C7C5"/>
         </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF8FAFD"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="2"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="medium">
-          <color rgb="FFC4C7C5"/>
-        </left>
-        <right style="medium">
-          <color rgb="FFC4C7C5"/>
-        </right>
-        <top/>
-        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -4260,6 +6563,66 @@
         </bottom>
       </border>
     </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF8FAFD"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="2"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF8FAFD"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="2"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="medium">
+          <color rgb="FFC4C7C5"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFC4C7C5"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -4274,20 +6637,20 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{25C3533C-F9CC-204C-AA03-16C84F66AF8E}" name="Table1" displayName="Table1" ref="A1:K101" totalsRowShown="0" headerRowDxfId="12" dataDxfId="1" headerRowBorderDxfId="13" tableBorderDxfId="14">
-  <autoFilter ref="A1:K101" xr:uid="{25C3533C-F9CC-204C-AA03-16C84F66AF8E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{25C3533C-F9CC-204C-AA03-16C84F66AF8E}" name="Table1" displayName="Table1" ref="A1:K201" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13" headerRowBorderDxfId="11" tableBorderDxfId="12">
+  <autoFilter ref="A1:K201" xr:uid="{25C3533C-F9CC-204C-AA03-16C84F66AF8E}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{07F8DED8-7A46-DD4F-AEC7-4DE64179538D}" name="م" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{B5F3020E-5356-AB4A-971D-DFB6B78C1101}" name="اسم الشركة المحتملة" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{BBC0132D-7A60-334F-B32A-72D4C74DE7EF}" name="النشاط اللوجستي التفصيلي" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{D934E27A-AC88-8741-824B-EC0AD3F18A43}" name="المحافظة والمنطقة الجغرافية" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{230B85F3-A417-454D-8B74-13DB5582B488}" name="الميناء المفضل" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{5CAEAA4E-CED6-2441-8C02-903FDC77E738}" name="هاتف التواصل" dataDxfId="0"/>
-    <tableColumn id="7" xr3:uid="{A7255D4C-B8FD-B244-BFC8-1C8D0ED743C6}" name="المسئول وصفته" dataDxfId="6"/>
-    <tableColumn id="8" xr3:uid="{0D8E16FF-FD35-0843-87CA-DCCD25210ADE}" name="البريد الإلكتروني للمسئول" dataDxfId="5"/>
-    <tableColumn id="9" xr3:uid="{FFC5DFF5-9E29-0143-9667-007F7383BFB5}" name="القطاع" dataDxfId="4"/>
-    <tableColumn id="10" xr3:uid="{BF870EB4-3286-DE47-A9BA-A442834CE3BA}" name="التوكيل الملاحي المفضل" dataDxfId="3"/>
-    <tableColumn id="11" xr3:uid="{B7921740-C9C6-3045-BCE8-B2DA1B4324FC}" name="شركة النقل الداخلي المتعاقد معها" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{07F8DED8-7A46-DD4F-AEC7-4DE64179538D}" name="م" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{B5F3020E-5356-AB4A-971D-DFB6B78C1101}" name="اسم الشركة المحتملة" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{BBC0132D-7A60-334F-B32A-72D4C74DE7EF}" name="النشاط اللوجستي التفصيلي" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{D934E27A-AC88-8741-824B-EC0AD3F18A43}" name="المحافظة والمنطقة الجغرافية" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{230B85F3-A417-454D-8B74-13DB5582B488}" name="الميناء المفضل" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{5CAEAA4E-CED6-2441-8C02-903FDC77E738}" name="هاتف التواصل" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{A7255D4C-B8FD-B244-BFC8-1C8D0ED743C6}" name="المسئول وصفته" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{0D8E16FF-FD35-0843-87CA-DCCD25210ADE}" name="البريد الإلكتروني للمسئول" dataDxfId="3"/>
+    <tableColumn id="9" xr3:uid="{FFC5DFF5-9E29-0143-9667-007F7383BFB5}" name="القطاع" dataDxfId="2"/>
+    <tableColumn id="10" xr3:uid="{BF870EB4-3286-DE47-A9BA-A442834CE3BA}" name="التوكيل الملاحي المفضل" dataDxfId="1"/>
+    <tableColumn id="11" xr3:uid="{B7921740-C9C6-3045-BCE8-B2DA1B4324FC}" name="شركة النقل الداخلي المتعاقد معها" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4610,7 +6973,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{177A7006-2706-E645-B507-1A7A29A9B608}">
-  <dimension ref="A1:K101"/>
+  <dimension ref="A1:K201"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="24.6640625" defaultRowHeight="48" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.1640625" customWidth="1"/>
@@ -4654,178 +7017,178 @@
         <v>386</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="8">
+    <row r="2" spans="1:11" s="18" customFormat="1" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="15">
         <v>1</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="15" t="s">
         <v>397</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F2" s="16">
         <v>100116039630</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="9" t="s">
+      <c r="I2" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="J2" s="9" t="s">
+      <c r="J2" s="17" t="s">
         <v>398</v>
       </c>
-      <c r="K2" s="9" t="s">
+      <c r="K2" s="17" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8">
+    <row r="3" spans="1:11" s="22" customFormat="1" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="19">
         <v>2</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="19" t="s">
         <v>400</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="I3" s="21" t="s">
         <v>98</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="J3" s="21" t="s">
         <v>387</v>
       </c>
-      <c r="K3" s="9" t="s">
+      <c r="K3" s="21" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="8">
+    <row r="4" spans="1:11" s="18" customFormat="1" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="15">
         <v>3</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="15" t="s">
         <v>402</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="G4" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="H4" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="I4" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="J4" s="9" t="s">
+      <c r="J4" s="17" t="s">
         <v>388</v>
       </c>
-      <c r="K4" s="9" t="s">
+      <c r="K4" s="17" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="8">
+    <row r="5" spans="1:11" s="22" customFormat="1" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="19">
         <v>4</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="19" t="s">
         <v>404</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="20">
         <v>102080705831</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="G5" s="19" t="s">
         <v>405</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="H5" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="I5" s="9" t="s">
+      <c r="I5" s="21" t="s">
         <v>98</v>
       </c>
-      <c r="J5" s="9" t="s">
+      <c r="J5" s="21" t="s">
         <v>389</v>
       </c>
-      <c r="K5" s="9" t="s">
+      <c r="K5" s="21" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="8">
+    <row r="6" spans="1:11" s="18" customFormat="1" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="15">
         <v>5</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="15" t="s">
         <v>407</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" s="15" t="s">
         <v>408</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="H6" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="I6" s="9" t="s">
+      <c r="I6" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="J6" s="9" t="s">
+      <c r="J6" s="17" t="s">
         <v>390</v>
       </c>
-      <c r="K6" s="9" t="s">
+      <c r="K6" s="17" t="s">
         <v>391</v>
       </c>
     </row>
@@ -8152,6 +10515,3306 @@
       </c>
       <c r="K101" s="3" t="s">
         <v>529</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="9">
+        <v>1</v>
+      </c>
+      <c r="B102" s="8" t="s">
+        <v>547</v>
+      </c>
+      <c r="C102" s="8" t="s">
+        <v>561</v>
+      </c>
+      <c r="D102" s="8" t="s">
+        <v>564</v>
+      </c>
+      <c r="E102" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F102" s="4">
+        <v>20453252525</v>
+      </c>
+      <c r="G102" s="8" t="s">
+        <v>565</v>
+      </c>
+      <c r="H102" s="8" t="s">
+        <v>566</v>
+      </c>
+      <c r="I102" s="8"/>
+      <c r="J102" s="8" t="s">
+        <v>562</v>
+      </c>
+      <c r="K102" s="8" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="9">
+        <v>2</v>
+      </c>
+      <c r="B103" s="8" t="s">
+        <v>548</v>
+      </c>
+      <c r="C103" s="8" t="s">
+        <v>567</v>
+      </c>
+      <c r="D103" s="8" t="s">
+        <v>568</v>
+      </c>
+      <c r="E103" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F103" s="4">
+        <v>20452738200</v>
+      </c>
+      <c r="G103" s="8" t="s">
+        <v>569</v>
+      </c>
+      <c r="H103" s="8" t="s">
+        <v>570</v>
+      </c>
+      <c r="I103" s="8"/>
+      <c r="J103" s="8" t="s">
+        <v>387</v>
+      </c>
+      <c r="K103" s="8" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="9">
+        <v>3</v>
+      </c>
+      <c r="B104" s="8" t="s">
+        <v>549</v>
+      </c>
+      <c r="C104" s="8" t="s">
+        <v>571</v>
+      </c>
+      <c r="D104" s="8" t="s">
+        <v>572</v>
+      </c>
+      <c r="E104" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F104" s="4">
+        <v>201222184718</v>
+      </c>
+      <c r="G104" s="8" t="s">
+        <v>573</v>
+      </c>
+      <c r="H104" s="8" t="s">
+        <v>574</v>
+      </c>
+      <c r="I104" s="8"/>
+      <c r="J104" s="8" t="s">
+        <v>388</v>
+      </c>
+      <c r="K104" s="8" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="9">
+        <v>4</v>
+      </c>
+      <c r="B105" s="8" t="s">
+        <v>550</v>
+      </c>
+      <c r="C105" s="8" t="s">
+        <v>642</v>
+      </c>
+      <c r="D105" s="8" t="s">
+        <v>576</v>
+      </c>
+      <c r="E105" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F105" s="4">
+        <v>201000580602</v>
+      </c>
+      <c r="G105" s="8" t="s">
+        <v>577</v>
+      </c>
+      <c r="H105" s="8" t="s">
+        <v>578</v>
+      </c>
+      <c r="I105" s="8"/>
+      <c r="J105" s="8" t="s">
+        <v>389</v>
+      </c>
+      <c r="K105" s="8" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="9">
+        <v>5</v>
+      </c>
+      <c r="B106" s="8" t="s">
+        <v>580</v>
+      </c>
+      <c r="C106" s="8" t="s">
+        <v>581</v>
+      </c>
+      <c r="D106" s="8" t="s">
+        <v>582</v>
+      </c>
+      <c r="E106" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F106" s="4">
+        <v>201227715151</v>
+      </c>
+      <c r="G106" s="8" t="s">
+        <v>583</v>
+      </c>
+      <c r="H106" s="8" t="s">
+        <v>584</v>
+      </c>
+      <c r="I106" s="8"/>
+      <c r="J106" s="8" t="s">
+        <v>390</v>
+      </c>
+      <c r="K106" s="8" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="9">
+        <v>6</v>
+      </c>
+      <c r="B107" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="C107" s="8" t="s">
+        <v>586</v>
+      </c>
+      <c r="D107" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="E107" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F107" s="4">
+        <v>201003241122</v>
+      </c>
+      <c r="G107" s="8" t="s">
+        <v>587</v>
+      </c>
+      <c r="H107" s="8" t="s">
+        <v>588</v>
+      </c>
+      <c r="I107" s="8"/>
+      <c r="J107" s="8" t="s">
+        <v>387</v>
+      </c>
+      <c r="K107" s="8" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="9">
+        <v>7</v>
+      </c>
+      <c r="B108" s="8" t="s">
+        <v>590</v>
+      </c>
+      <c r="C108" s="8" t="s">
+        <v>591</v>
+      </c>
+      <c r="D108" s="8" t="s">
+        <v>592</v>
+      </c>
+      <c r="E108" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F108" s="4">
+        <v>201000217261</v>
+      </c>
+      <c r="G108" s="8" t="s">
+        <v>593</v>
+      </c>
+      <c r="H108" s="8" t="s">
+        <v>594</v>
+      </c>
+      <c r="I108" s="8"/>
+      <c r="J108" s="8" t="s">
+        <v>388</v>
+      </c>
+      <c r="K108" s="8" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="9">
+        <v>8</v>
+      </c>
+      <c r="B109" s="8" t="s">
+        <v>595</v>
+      </c>
+      <c r="C109" s="8" t="s">
+        <v>596</v>
+      </c>
+      <c r="D109" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="E109" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F109" s="4">
+        <v>201003241122</v>
+      </c>
+      <c r="G109" s="8" t="s">
+        <v>597</v>
+      </c>
+      <c r="H109" s="8" t="s">
+        <v>598</v>
+      </c>
+      <c r="I109" s="8"/>
+      <c r="J109" s="8" t="s">
+        <v>389</v>
+      </c>
+      <c r="K109" s="8" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="9">
+        <v>9</v>
+      </c>
+      <c r="B110" s="8" t="s">
+        <v>599</v>
+      </c>
+      <c r="C110" s="8" t="s">
+        <v>600</v>
+      </c>
+      <c r="D110" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="E110" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F110" s="4">
+        <v>201222143000</v>
+      </c>
+      <c r="G110" s="8" t="s">
+        <v>601</v>
+      </c>
+      <c r="H110" s="8" t="s">
+        <v>602</v>
+      </c>
+      <c r="I110" s="8"/>
+      <c r="J110" s="8" t="s">
+        <v>390</v>
+      </c>
+      <c r="K110" s="8" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="9">
+        <v>10</v>
+      </c>
+      <c r="B111" s="8" t="s">
+        <v>552</v>
+      </c>
+      <c r="C111" s="8" t="s">
+        <v>603</v>
+      </c>
+      <c r="D111" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E111" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F111" s="4">
+        <v>201060919100</v>
+      </c>
+      <c r="G111" s="8" t="s">
+        <v>604</v>
+      </c>
+      <c r="H111" s="8" t="s">
+        <v>605</v>
+      </c>
+      <c r="I111" s="8"/>
+      <c r="J111" s="8" t="s">
+        <v>387</v>
+      </c>
+      <c r="K111" s="8" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="9">
+        <v>11</v>
+      </c>
+      <c r="B112" s="8" t="s">
+        <v>553</v>
+      </c>
+      <c r="C112" s="8" t="s">
+        <v>606</v>
+      </c>
+      <c r="D112" s="8" t="s">
+        <v>568</v>
+      </c>
+      <c r="E112" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F112" s="4">
+        <v>201010200604</v>
+      </c>
+      <c r="G112" s="8" t="s">
+        <v>607</v>
+      </c>
+      <c r="H112" s="8" t="s">
+        <v>608</v>
+      </c>
+      <c r="I112" s="8"/>
+      <c r="J112" s="8" t="s">
+        <v>388</v>
+      </c>
+      <c r="K112" s="8" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="9">
+        <v>12</v>
+      </c>
+      <c r="B113" s="8" t="s">
+        <v>554</v>
+      </c>
+      <c r="C113" s="8" t="s">
+        <v>610</v>
+      </c>
+      <c r="D113" s="8" t="s">
+        <v>611</v>
+      </c>
+      <c r="E113" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F113" s="4">
+        <v>201222159162</v>
+      </c>
+      <c r="G113" s="8" t="s">
+        <v>612</v>
+      </c>
+      <c r="H113" s="8" t="s">
+        <v>613</v>
+      </c>
+      <c r="I113" s="8"/>
+      <c r="J113" s="8" t="s">
+        <v>389</v>
+      </c>
+      <c r="K113" s="8" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="9">
+        <v>13</v>
+      </c>
+      <c r="B114" s="8" t="s">
+        <v>555</v>
+      </c>
+      <c r="C114" s="8" t="s">
+        <v>614</v>
+      </c>
+      <c r="D114" s="8" t="s">
+        <v>643</v>
+      </c>
+      <c r="E114" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F114" s="4">
+        <v>201025076667</v>
+      </c>
+      <c r="G114" s="8" t="s">
+        <v>615</v>
+      </c>
+      <c r="H114" s="8" t="s">
+        <v>616</v>
+      </c>
+      <c r="I114" s="8"/>
+      <c r="J114" s="8" t="s">
+        <v>390</v>
+      </c>
+      <c r="K114" s="8" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="9">
+        <v>14</v>
+      </c>
+      <c r="B115" s="8" t="s">
+        <v>617</v>
+      </c>
+      <c r="C115" s="8" t="s">
+        <v>618</v>
+      </c>
+      <c r="D115" s="8" t="s">
+        <v>644</v>
+      </c>
+      <c r="E115" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F115" s="4">
+        <v>201223215655</v>
+      </c>
+      <c r="G115" s="8" t="s">
+        <v>619</v>
+      </c>
+      <c r="H115" s="8" t="s">
+        <v>620</v>
+      </c>
+      <c r="I115" s="8"/>
+      <c r="J115" s="8" t="s">
+        <v>387</v>
+      </c>
+      <c r="K115" s="8" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="9">
+        <v>15</v>
+      </c>
+      <c r="B116" s="8" t="s">
+        <v>621</v>
+      </c>
+      <c r="C116" s="8" t="s">
+        <v>622</v>
+      </c>
+      <c r="D116" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E116" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F116" s="4">
+        <v>20128935561120</v>
+      </c>
+      <c r="G116" s="8" t="s">
+        <v>623</v>
+      </c>
+      <c r="H116" s="8" t="s">
+        <v>624</v>
+      </c>
+      <c r="I116" s="8"/>
+      <c r="J116" s="8" t="s">
+        <v>388</v>
+      </c>
+      <c r="K116" s="8" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="9">
+        <v>16</v>
+      </c>
+      <c r="B117" s="8" t="s">
+        <v>556</v>
+      </c>
+      <c r="C117" s="8" t="s">
+        <v>625</v>
+      </c>
+      <c r="D117" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="E117" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F117" s="4">
+        <v>201222140301</v>
+      </c>
+      <c r="G117" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="H117" s="8" t="s">
+        <v>627</v>
+      </c>
+      <c r="I117" s="8"/>
+      <c r="J117" s="8" t="s">
+        <v>389</v>
+      </c>
+      <c r="K117" s="8" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="9">
+        <v>17</v>
+      </c>
+      <c r="B118" s="8" t="s">
+        <v>557</v>
+      </c>
+      <c r="C118" s="8" t="s">
+        <v>628</v>
+      </c>
+      <c r="D118" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="E118" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F118" s="4">
+        <v>201116114430</v>
+      </c>
+      <c r="G118" s="8" t="s">
+        <v>629</v>
+      </c>
+      <c r="H118" s="8" t="s">
+        <v>630</v>
+      </c>
+      <c r="I118" s="8"/>
+      <c r="J118" s="8" t="s">
+        <v>390</v>
+      </c>
+      <c r="K118" s="8" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="9">
+        <v>18</v>
+      </c>
+      <c r="B119" s="8" t="s">
+        <v>558</v>
+      </c>
+      <c r="C119" s="8" t="s">
+        <v>631</v>
+      </c>
+      <c r="D119" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E119" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F119" s="4">
+        <v>20452319520</v>
+      </c>
+      <c r="G119" s="8" t="s">
+        <v>632</v>
+      </c>
+      <c r="H119" s="8" t="s">
+        <v>633</v>
+      </c>
+      <c r="I119" s="8"/>
+      <c r="J119" s="8" t="s">
+        <v>387</v>
+      </c>
+      <c r="K119" s="8" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="9">
+        <v>19</v>
+      </c>
+      <c r="B120" s="8" t="s">
+        <v>559</v>
+      </c>
+      <c r="C120" s="8" t="s">
+        <v>634</v>
+      </c>
+      <c r="D120" s="8" t="s">
+        <v>635</v>
+      </c>
+      <c r="E120" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F120" s="4">
+        <v>201282500500</v>
+      </c>
+      <c r="G120" s="8" t="s">
+        <v>636</v>
+      </c>
+      <c r="H120" s="8" t="s">
+        <v>637</v>
+      </c>
+      <c r="I120" s="8"/>
+      <c r="J120" s="8" t="s">
+        <v>388</v>
+      </c>
+      <c r="K120" s="8" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="3">
+        <v>20</v>
+      </c>
+      <c r="B121" s="11" t="s">
+        <v>560</v>
+      </c>
+      <c r="C121" s="11" t="s">
+        <v>638</v>
+      </c>
+      <c r="D121" s="11" t="s">
+        <v>639</v>
+      </c>
+      <c r="E121" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="F121" s="23">
+        <v>201003194050</v>
+      </c>
+      <c r="G121" s="11" t="s">
+        <v>640</v>
+      </c>
+      <c r="H121" s="11" t="s">
+        <v>641</v>
+      </c>
+      <c r="I121" s="8"/>
+      <c r="J121" s="8" t="s">
+        <v>389</v>
+      </c>
+      <c r="K121" s="11" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="9">
+        <v>21</v>
+      </c>
+      <c r="B122" s="8" t="s">
+        <v>646</v>
+      </c>
+      <c r="C122" s="8" t="s">
+        <v>647</v>
+      </c>
+      <c r="D122" s="8" t="s">
+        <v>712</v>
+      </c>
+      <c r="E122" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F122" s="4">
+        <v>10222679105</v>
+      </c>
+      <c r="G122" s="8" t="s">
+        <v>727</v>
+      </c>
+      <c r="H122" s="8" t="s">
+        <v>730</v>
+      </c>
+      <c r="I122" s="8"/>
+      <c r="J122" s="8" t="s">
+        <v>390</v>
+      </c>
+      <c r="K122" s="8" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="9">
+        <v>22</v>
+      </c>
+      <c r="B123" s="8" t="s">
+        <v>648</v>
+      </c>
+      <c r="C123" s="8" t="s">
+        <v>649</v>
+      </c>
+      <c r="D123" s="8" t="s">
+        <v>713</v>
+      </c>
+      <c r="E123" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F123" s="4">
+        <v>10017816405</v>
+      </c>
+      <c r="G123" s="8" t="s">
+        <v>728</v>
+      </c>
+      <c r="H123" s="8" t="s">
+        <v>731</v>
+      </c>
+      <c r="I123" s="8"/>
+      <c r="J123" s="8" t="s">
+        <v>387</v>
+      </c>
+      <c r="K123" s="8" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A124" s="9">
+        <v>23</v>
+      </c>
+      <c r="B124" s="8" t="s">
+        <v>650</v>
+      </c>
+      <c r="C124" s="8" t="s">
+        <v>708</v>
+      </c>
+      <c r="D124" s="8" t="s">
+        <v>714</v>
+      </c>
+      <c r="E124" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F124" s="4">
+        <v>10025890525</v>
+      </c>
+      <c r="G124" s="8" t="s">
+        <v>729</v>
+      </c>
+      <c r="H124" s="8" t="s">
+        <v>732</v>
+      </c>
+      <c r="I124" s="8"/>
+      <c r="J124" s="8" t="s">
+        <v>388</v>
+      </c>
+      <c r="K124" s="8" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A125" s="9">
+        <v>24</v>
+      </c>
+      <c r="B125" s="8" t="s">
+        <v>652</v>
+      </c>
+      <c r="C125" s="8" t="s">
+        <v>653</v>
+      </c>
+      <c r="D125" s="8" t="s">
+        <v>713</v>
+      </c>
+      <c r="E125" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F125" s="4">
+        <v>202382040015</v>
+      </c>
+      <c r="G125" s="8" t="s">
+        <v>654</v>
+      </c>
+      <c r="H125" s="8" t="s">
+        <v>733</v>
+      </c>
+      <c r="I125" s="8"/>
+      <c r="J125" s="8" t="s">
+        <v>389</v>
+      </c>
+      <c r="K125" s="8" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="9">
+        <v>25</v>
+      </c>
+      <c r="B126" s="8" t="s">
+        <v>655</v>
+      </c>
+      <c r="C126" s="8" t="s">
+        <v>656</v>
+      </c>
+      <c r="D126" s="8" t="s">
+        <v>715</v>
+      </c>
+      <c r="E126" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F126" s="4">
+        <v>10066660285</v>
+      </c>
+      <c r="G126" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="H126" s="8" t="s">
+        <v>734</v>
+      </c>
+      <c r="I126" s="8"/>
+      <c r="J126" s="8" t="s">
+        <v>390</v>
+      </c>
+      <c r="K126" s="8" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="127" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A127" s="9">
+        <v>26</v>
+      </c>
+      <c r="B127" s="8" t="s">
+        <v>659</v>
+      </c>
+      <c r="C127" s="8" t="s">
+        <v>660</v>
+      </c>
+      <c r="D127" s="8" t="s">
+        <v>716</v>
+      </c>
+      <c r="E127" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F127" s="4">
+        <v>10950035955</v>
+      </c>
+      <c r="G127" s="8" t="s">
+        <v>661</v>
+      </c>
+      <c r="H127" s="8" t="s">
+        <v>735</v>
+      </c>
+      <c r="I127" s="8"/>
+      <c r="J127" s="8" t="s">
+        <v>387</v>
+      </c>
+      <c r="K127" s="8" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A128" s="9">
+        <v>27</v>
+      </c>
+      <c r="B128" s="8" t="s">
+        <v>663</v>
+      </c>
+      <c r="C128" s="8" t="s">
+        <v>664</v>
+      </c>
+      <c r="D128" s="8" t="s">
+        <v>717</v>
+      </c>
+      <c r="E128" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F128" s="4">
+        <v>10010836965</v>
+      </c>
+      <c r="G128" s="8" t="s">
+        <v>665</v>
+      </c>
+      <c r="H128" s="8" t="s">
+        <v>736</v>
+      </c>
+      <c r="I128" s="8"/>
+      <c r="J128" s="8" t="s">
+        <v>388</v>
+      </c>
+      <c r="K128" s="8" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A129" s="9">
+        <v>28</v>
+      </c>
+      <c r="B129" s="8" t="s">
+        <v>666</v>
+      </c>
+      <c r="C129" s="8" t="s">
+        <v>667</v>
+      </c>
+      <c r="D129" s="8" t="s">
+        <v>718</v>
+      </c>
+      <c r="E129" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F129" s="4">
+        <v>10024088705</v>
+      </c>
+      <c r="G129" s="8" t="s">
+        <v>668</v>
+      </c>
+      <c r="H129" s="8" t="s">
+        <v>737</v>
+      </c>
+      <c r="I129" s="8"/>
+      <c r="J129" s="8" t="s">
+        <v>389</v>
+      </c>
+      <c r="K129" s="8" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="130" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A130" s="9">
+        <v>29</v>
+      </c>
+      <c r="B130" s="8" t="s">
+        <v>670</v>
+      </c>
+      <c r="C130" s="8" t="s">
+        <v>709</v>
+      </c>
+      <c r="D130" s="8" t="s">
+        <v>719</v>
+      </c>
+      <c r="E130" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F130" s="4">
+        <v>12877087205</v>
+      </c>
+      <c r="G130" s="8" t="s">
+        <v>671</v>
+      </c>
+      <c r="H130" s="8" t="s">
+        <v>738</v>
+      </c>
+      <c r="I130" s="8"/>
+      <c r="J130" s="8" t="s">
+        <v>390</v>
+      </c>
+      <c r="K130" s="8" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="131" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A131" s="9">
+        <v>30</v>
+      </c>
+      <c r="B131" s="8" t="s">
+        <v>672</v>
+      </c>
+      <c r="C131" s="8" t="s">
+        <v>710</v>
+      </c>
+      <c r="D131" s="8" t="s">
+        <v>720</v>
+      </c>
+      <c r="E131" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F131" s="4">
+        <v>10025512955</v>
+      </c>
+      <c r="G131" s="8" t="s">
+        <v>673</v>
+      </c>
+      <c r="H131" s="8" t="s">
+        <v>739</v>
+      </c>
+      <c r="I131" s="8"/>
+      <c r="J131" s="8" t="s">
+        <v>387</v>
+      </c>
+      <c r="K131" s="8" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A132" s="9">
+        <v>31</v>
+      </c>
+      <c r="B132" s="8" t="s">
+        <v>674</v>
+      </c>
+      <c r="C132" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="D132" s="8" t="s">
+        <v>721</v>
+      </c>
+      <c r="E132" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F132" s="4">
+        <v>10000584775</v>
+      </c>
+      <c r="G132" s="8" t="s">
+        <v>676</v>
+      </c>
+      <c r="H132" s="8" t="s">
+        <v>740</v>
+      </c>
+      <c r="I132" s="8"/>
+      <c r="J132" s="8" t="s">
+        <v>388</v>
+      </c>
+      <c r="K132" s="8" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="133" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A133" s="9">
+        <v>32</v>
+      </c>
+      <c r="B133" s="8" t="s">
+        <v>677</v>
+      </c>
+      <c r="C133" s="8" t="s">
+        <v>678</v>
+      </c>
+      <c r="D133" s="8" t="s">
+        <v>722</v>
+      </c>
+      <c r="E133" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F133" s="4">
+        <v>10033387275</v>
+      </c>
+      <c r="G133" s="8" t="s">
+        <v>679</v>
+      </c>
+      <c r="H133" s="8" t="s">
+        <v>741</v>
+      </c>
+      <c r="I133" s="8"/>
+      <c r="J133" s="8" t="s">
+        <v>388</v>
+      </c>
+      <c r="K133" s="8" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="134" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A134" s="9">
+        <v>33</v>
+      </c>
+      <c r="B134" s="8" t="s">
+        <v>681</v>
+      </c>
+      <c r="C134" s="8" t="s">
+        <v>682</v>
+      </c>
+      <c r="D134" s="8" t="s">
+        <v>723</v>
+      </c>
+      <c r="E134" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F134" s="4">
+        <v>10663102085</v>
+      </c>
+      <c r="G134" s="8" t="s">
+        <v>683</v>
+      </c>
+      <c r="H134" s="8" t="s">
+        <v>742</v>
+      </c>
+      <c r="I134" s="8"/>
+      <c r="J134" s="8" t="s">
+        <v>392</v>
+      </c>
+      <c r="K134" s="8" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="135" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A135" s="9">
+        <v>34</v>
+      </c>
+      <c r="B135" s="8" t="s">
+        <v>685</v>
+      </c>
+      <c r="C135" s="8" t="s">
+        <v>686</v>
+      </c>
+      <c r="D135" s="8" t="s">
+        <v>714</v>
+      </c>
+      <c r="E135" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F135" s="4">
+        <v>10016047845</v>
+      </c>
+      <c r="G135" s="8" t="s">
+        <v>687</v>
+      </c>
+      <c r="H135" s="8" t="s">
+        <v>743</v>
+      </c>
+      <c r="I135" s="8"/>
+      <c r="J135" s="8" t="s">
+        <v>389</v>
+      </c>
+      <c r="K135" s="8" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="136" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A136" s="9">
+        <v>35</v>
+      </c>
+      <c r="B136" s="8" t="s">
+        <v>688</v>
+      </c>
+      <c r="C136" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="D136" s="8" t="s">
+        <v>724</v>
+      </c>
+      <c r="E136" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F136" s="4">
+        <v>10052877225</v>
+      </c>
+      <c r="G136" s="8" t="s">
+        <v>689</v>
+      </c>
+      <c r="H136" s="8" t="s">
+        <v>744</v>
+      </c>
+      <c r="I136" s="8"/>
+      <c r="J136" s="8" t="s">
+        <v>390</v>
+      </c>
+      <c r="K136" s="8" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="137" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A137" s="9">
+        <v>36</v>
+      </c>
+      <c r="B137" s="8" t="s">
+        <v>690</v>
+      </c>
+      <c r="C137" s="8" t="s">
+        <v>691</v>
+      </c>
+      <c r="D137" s="8" t="s">
+        <v>725</v>
+      </c>
+      <c r="E137" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F137" s="4">
+        <v>10209009085</v>
+      </c>
+      <c r="G137" s="8" t="s">
+        <v>692</v>
+      </c>
+      <c r="H137" s="8" t="s">
+        <v>745</v>
+      </c>
+      <c r="I137" s="8"/>
+      <c r="J137" s="8" t="s">
+        <v>387</v>
+      </c>
+      <c r="K137" s="8" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="138" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A138" s="9">
+        <v>37</v>
+      </c>
+      <c r="B138" s="8" t="s">
+        <v>693</v>
+      </c>
+      <c r="C138" s="8" t="s">
+        <v>694</v>
+      </c>
+      <c r="D138" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="E138" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F138" s="4">
+        <v>1222140301</v>
+      </c>
+      <c r="G138" s="8" t="s">
+        <v>695</v>
+      </c>
+      <c r="H138" s="8" t="s">
+        <v>627</v>
+      </c>
+      <c r="I138" s="8"/>
+      <c r="J138" s="8" t="s">
+        <v>390</v>
+      </c>
+      <c r="K138" s="8" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="139" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A139" s="9">
+        <v>38</v>
+      </c>
+      <c r="B139" s="8" t="s">
+        <v>696</v>
+      </c>
+      <c r="C139" s="8" t="s">
+        <v>697</v>
+      </c>
+      <c r="D139" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="E139" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F139" s="4">
+        <v>1143399993</v>
+      </c>
+      <c r="G139" s="8" t="s">
+        <v>698</v>
+      </c>
+      <c r="H139" s="8" t="s">
+        <v>699</v>
+      </c>
+      <c r="I139" s="8"/>
+      <c r="J139" s="8" t="s">
+        <v>389</v>
+      </c>
+      <c r="K139" s="8" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="140" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A140" s="9">
+        <v>39</v>
+      </c>
+      <c r="B140" s="8" t="s">
+        <v>700</v>
+      </c>
+      <c r="C140" s="8" t="s">
+        <v>701</v>
+      </c>
+      <c r="D140" s="8" t="s">
+        <v>726</v>
+      </c>
+      <c r="E140" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F140" s="4">
+        <v>10010446003</v>
+      </c>
+      <c r="G140" s="8" t="s">
+        <v>702</v>
+      </c>
+      <c r="H140" s="8" t="s">
+        <v>746</v>
+      </c>
+      <c r="I140" s="8"/>
+      <c r="J140" s="8" t="s">
+        <v>387</v>
+      </c>
+      <c r="K140" s="8" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="141" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A141" s="3">
+        <v>40</v>
+      </c>
+      <c r="B141" s="11" t="s">
+        <v>703</v>
+      </c>
+      <c r="C141" s="11" t="s">
+        <v>704</v>
+      </c>
+      <c r="D141" s="11" t="s">
+        <v>705</v>
+      </c>
+      <c r="E141" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F141" s="23">
+        <v>1006792338</v>
+      </c>
+      <c r="G141" s="11" t="s">
+        <v>706</v>
+      </c>
+      <c r="H141" s="11" t="s">
+        <v>707</v>
+      </c>
+      <c r="I141" s="8"/>
+      <c r="J141" s="8" t="s">
+        <v>388</v>
+      </c>
+      <c r="K141" s="11" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="142" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A142" s="9">
+        <v>41</v>
+      </c>
+      <c r="B142" s="8" t="s">
+        <v>750</v>
+      </c>
+      <c r="C142" s="8" t="s">
+        <v>751</v>
+      </c>
+      <c r="D142" s="8" t="s">
+        <v>840</v>
+      </c>
+      <c r="E142" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F142" s="4">
+        <v>1222166302</v>
+      </c>
+      <c r="G142" s="8" t="s">
+        <v>845</v>
+      </c>
+      <c r="H142" s="8" t="s">
+        <v>846</v>
+      </c>
+      <c r="I142" s="8"/>
+      <c r="J142" s="8" t="s">
+        <v>390</v>
+      </c>
+      <c r="K142" s="8" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="143" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A143" s="9">
+        <v>42</v>
+      </c>
+      <c r="B143" s="8" t="s">
+        <v>753</v>
+      </c>
+      <c r="C143" s="8" t="s">
+        <v>754</v>
+      </c>
+      <c r="D143" s="8" t="s">
+        <v>841</v>
+      </c>
+      <c r="E143" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F143" s="4">
+        <v>1222249017</v>
+      </c>
+      <c r="G143" s="8" t="s">
+        <v>755</v>
+      </c>
+      <c r="H143" s="8" t="s">
+        <v>756</v>
+      </c>
+      <c r="I143" s="8"/>
+      <c r="J143" s="8" t="s">
+        <v>387</v>
+      </c>
+      <c r="K143" s="8" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="144" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A144" s="9">
+        <v>43</v>
+      </c>
+      <c r="B144" s="8" t="s">
+        <v>758</v>
+      </c>
+      <c r="C144" s="8" t="s">
+        <v>759</v>
+      </c>
+      <c r="D144" s="8" t="s">
+        <v>842</v>
+      </c>
+      <c r="E144" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F144" s="4">
+        <v>1005660809</v>
+      </c>
+      <c r="G144" s="8" t="s">
+        <v>760</v>
+      </c>
+      <c r="H144" s="8" t="s">
+        <v>761</v>
+      </c>
+      <c r="I144" s="8"/>
+      <c r="J144" s="8" t="s">
+        <v>388</v>
+      </c>
+      <c r="K144" s="8" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="145" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A145" s="9">
+        <v>44</v>
+      </c>
+      <c r="B145" s="8" t="s">
+        <v>763</v>
+      </c>
+      <c r="C145" s="8" t="s">
+        <v>764</v>
+      </c>
+      <c r="D145" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="E145" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F145" s="4">
+        <v>1001234520</v>
+      </c>
+      <c r="G145" s="8" t="s">
+        <v>765</v>
+      </c>
+      <c r="H145" s="8" t="s">
+        <v>766</v>
+      </c>
+      <c r="I145" s="8"/>
+      <c r="J145" s="8" t="s">
+        <v>389</v>
+      </c>
+      <c r="K145" s="8" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="146" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A146" s="9">
+        <v>45</v>
+      </c>
+      <c r="B146" s="8" t="s">
+        <v>768</v>
+      </c>
+      <c r="C146" s="8" t="s">
+        <v>769</v>
+      </c>
+      <c r="D146" s="8" t="s">
+        <v>770</v>
+      </c>
+      <c r="E146" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F146" s="4">
+        <v>1005011552</v>
+      </c>
+      <c r="G146" s="8" t="s">
+        <v>771</v>
+      </c>
+      <c r="H146" s="8" t="s">
+        <v>772</v>
+      </c>
+      <c r="I146" s="8"/>
+      <c r="J146" s="8" t="s">
+        <v>392</v>
+      </c>
+      <c r="K146" s="8" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="147" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A147" s="9">
+        <v>46</v>
+      </c>
+      <c r="B147" s="8" t="s">
+        <v>774</v>
+      </c>
+      <c r="C147" s="8" t="s">
+        <v>775</v>
+      </c>
+      <c r="D147" s="8" t="s">
+        <v>770</v>
+      </c>
+      <c r="E147" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F147" s="4">
+        <v>1001124008</v>
+      </c>
+      <c r="G147" s="8" t="s">
+        <v>776</v>
+      </c>
+      <c r="H147" s="8" t="s">
+        <v>777</v>
+      </c>
+      <c r="I147" s="8"/>
+      <c r="J147" s="8" t="s">
+        <v>390</v>
+      </c>
+      <c r="K147" s="8" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="148" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A148" s="9">
+        <v>47</v>
+      </c>
+      <c r="B148" s="8" t="s">
+        <v>778</v>
+      </c>
+      <c r="C148" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="D148" s="8" t="s">
+        <v>780</v>
+      </c>
+      <c r="E148" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F148" s="4">
+        <v>1001026064</v>
+      </c>
+      <c r="G148" s="8" t="s">
+        <v>781</v>
+      </c>
+      <c r="H148" s="8" t="s">
+        <v>782</v>
+      </c>
+      <c r="I148" s="8"/>
+      <c r="J148" s="8" t="s">
+        <v>387</v>
+      </c>
+      <c r="K148" s="8" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="149" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A149" s="9">
+        <v>48</v>
+      </c>
+      <c r="B149" s="8" t="s">
+        <v>783</v>
+      </c>
+      <c r="C149" s="8" t="s">
+        <v>784</v>
+      </c>
+      <c r="D149" s="8" t="s">
+        <v>785</v>
+      </c>
+      <c r="E149" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F149" s="4">
+        <v>10944320100</v>
+      </c>
+      <c r="G149" s="8" t="s">
+        <v>786</v>
+      </c>
+      <c r="H149" s="8" t="s">
+        <v>787</v>
+      </c>
+      <c r="I149" s="8"/>
+      <c r="J149" s="8" t="s">
+        <v>388</v>
+      </c>
+      <c r="K149" s="8" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="150" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A150" s="9">
+        <v>49</v>
+      </c>
+      <c r="B150" s="8" t="s">
+        <v>788</v>
+      </c>
+      <c r="C150" s="8" t="s">
+        <v>789</v>
+      </c>
+      <c r="D150" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="E150" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F150" s="4">
+        <v>1009878794</v>
+      </c>
+      <c r="G150" s="8" t="s">
+        <v>790</v>
+      </c>
+      <c r="H150" s="8" t="s">
+        <v>791</v>
+      </c>
+      <c r="I150" s="8"/>
+      <c r="J150" s="8" t="s">
+        <v>389</v>
+      </c>
+      <c r="K150" s="8" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="151" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A151" s="9">
+        <v>50</v>
+      </c>
+      <c r="B151" s="8" t="s">
+        <v>792</v>
+      </c>
+      <c r="C151" s="8" t="s">
+        <v>793</v>
+      </c>
+      <c r="D151" s="8" t="s">
+        <v>843</v>
+      </c>
+      <c r="E151" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F151" s="4">
+        <v>1223243881</v>
+      </c>
+      <c r="G151" s="8" t="s">
+        <v>794</v>
+      </c>
+      <c r="H151" s="8" t="s">
+        <v>795</v>
+      </c>
+      <c r="I151" s="8"/>
+      <c r="J151" s="8" t="s">
+        <v>387</v>
+      </c>
+      <c r="K151" s="8" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="152" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A152" s="9">
+        <v>51</v>
+      </c>
+      <c r="B152" s="8" t="s">
+        <v>796</v>
+      </c>
+      <c r="C152" s="8" t="s">
+        <v>797</v>
+      </c>
+      <c r="D152" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="E152" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F152" s="4">
+        <v>1066648244</v>
+      </c>
+      <c r="G152" s="8" t="s">
+        <v>798</v>
+      </c>
+      <c r="H152" s="8" t="s">
+        <v>799</v>
+      </c>
+      <c r="I152" s="8"/>
+      <c r="J152" s="8" t="s">
+        <v>390</v>
+      </c>
+      <c r="K152" s="8" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="153" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A153" s="9">
+        <v>52</v>
+      </c>
+      <c r="B153" s="8" t="s">
+        <v>800</v>
+      </c>
+      <c r="C153" s="8" t="s">
+        <v>801</v>
+      </c>
+      <c r="D153" s="8" t="s">
+        <v>770</v>
+      </c>
+      <c r="E153" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F153" s="4">
+        <v>1067555658</v>
+      </c>
+      <c r="G153" s="8" t="s">
+        <v>802</v>
+      </c>
+      <c r="H153" s="8" t="s">
+        <v>803</v>
+      </c>
+      <c r="I153" s="8"/>
+      <c r="J153" s="8" t="s">
+        <v>388</v>
+      </c>
+      <c r="K153" s="8" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="154" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A154" s="9">
+        <v>53</v>
+      </c>
+      <c r="B154" s="8" t="s">
+        <v>804</v>
+      </c>
+      <c r="C154" s="8" t="s">
+        <v>805</v>
+      </c>
+      <c r="D154" s="8" t="s">
+        <v>806</v>
+      </c>
+      <c r="E154" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F154" s="4">
+        <v>1223523607</v>
+      </c>
+      <c r="G154" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="H154" s="8" t="s">
+        <v>808</v>
+      </c>
+      <c r="I154" s="8"/>
+      <c r="J154" s="8" t="s">
+        <v>392</v>
+      </c>
+      <c r="K154" s="8" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="155" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A155" s="9">
+        <v>54</v>
+      </c>
+      <c r="B155" s="8" t="s">
+        <v>809</v>
+      </c>
+      <c r="C155" s="8" t="s">
+        <v>810</v>
+      </c>
+      <c r="D155" s="8" t="s">
+        <v>811</v>
+      </c>
+      <c r="E155" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F155" s="4">
+        <v>1009241557</v>
+      </c>
+      <c r="G155" s="8" t="s">
+        <v>812</v>
+      </c>
+      <c r="H155" s="8" t="s">
+        <v>813</v>
+      </c>
+      <c r="I155" s="8"/>
+      <c r="J155" s="8" t="s">
+        <v>390</v>
+      </c>
+      <c r="K155" s="8" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="156" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A156" s="9">
+        <v>55</v>
+      </c>
+      <c r="B156" s="8" t="s">
+        <v>814</v>
+      </c>
+      <c r="C156" s="8" t="s">
+        <v>815</v>
+      </c>
+      <c r="D156" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="E156" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F156" s="4">
+        <v>1063783146</v>
+      </c>
+      <c r="G156" s="8" t="s">
+        <v>816</v>
+      </c>
+      <c r="H156" s="8" t="s">
+        <v>817</v>
+      </c>
+      <c r="I156" s="8"/>
+      <c r="J156" s="8" t="s">
+        <v>387</v>
+      </c>
+      <c r="K156" s="8" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="157" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A157" s="9">
+        <v>56</v>
+      </c>
+      <c r="B157" s="8" t="s">
+        <v>818</v>
+      </c>
+      <c r="C157" s="8" t="s">
+        <v>819</v>
+      </c>
+      <c r="D157" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="E157" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F157" s="4">
+        <v>1001787346</v>
+      </c>
+      <c r="G157" s="8" t="s">
+        <v>820</v>
+      </c>
+      <c r="H157" s="8" t="s">
+        <v>821</v>
+      </c>
+      <c r="I157" s="8"/>
+      <c r="J157" s="8" t="s">
+        <v>388</v>
+      </c>
+      <c r="K157" s="8" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="158" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A158" s="9">
+        <v>57</v>
+      </c>
+      <c r="B158" s="8" t="s">
+        <v>822</v>
+      </c>
+      <c r="C158" s="8" t="s">
+        <v>823</v>
+      </c>
+      <c r="D158" s="8" t="s">
+        <v>361</v>
+      </c>
+      <c r="E158" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F158" s="4">
+        <v>1222137790</v>
+      </c>
+      <c r="G158" s="8" t="s">
+        <v>824</v>
+      </c>
+      <c r="H158" s="8" t="s">
+        <v>825</v>
+      </c>
+      <c r="I158" s="8"/>
+      <c r="J158" s="8" t="s">
+        <v>387</v>
+      </c>
+      <c r="K158" s="8" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="159" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A159" s="9">
+        <v>58</v>
+      </c>
+      <c r="B159" s="8" t="s">
+        <v>826</v>
+      </c>
+      <c r="C159" s="8" t="s">
+        <v>827</v>
+      </c>
+      <c r="D159" s="8" t="s">
+        <v>828</v>
+      </c>
+      <c r="E159" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F159" s="4">
+        <v>1223470189</v>
+      </c>
+      <c r="G159" s="8" t="s">
+        <v>829</v>
+      </c>
+      <c r="H159" s="8" t="s">
+        <v>830</v>
+      </c>
+      <c r="I159" s="8"/>
+      <c r="J159" s="8" t="s">
+        <v>390</v>
+      </c>
+      <c r="K159" s="8" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="160" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A160" s="9">
+        <v>59</v>
+      </c>
+      <c r="B160" s="8" t="s">
+        <v>831</v>
+      </c>
+      <c r="C160" s="8" t="s">
+        <v>832</v>
+      </c>
+      <c r="D160" s="8" t="s">
+        <v>833</v>
+      </c>
+      <c r="E160" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F160" s="4">
+        <v>1222164235</v>
+      </c>
+      <c r="G160" s="8" t="s">
+        <v>834</v>
+      </c>
+      <c r="H160" s="8" t="s">
+        <v>835</v>
+      </c>
+      <c r="I160" s="8"/>
+      <c r="J160" s="8" t="s">
+        <v>389</v>
+      </c>
+      <c r="K160" s="8" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="161" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A161" s="3">
+        <v>60</v>
+      </c>
+      <c r="B161" s="11" t="s">
+        <v>836</v>
+      </c>
+      <c r="C161" s="11" t="s">
+        <v>837</v>
+      </c>
+      <c r="D161" s="11" t="s">
+        <v>844</v>
+      </c>
+      <c r="E161" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F161" s="23">
+        <v>1227399551</v>
+      </c>
+      <c r="G161" s="11" t="s">
+        <v>838</v>
+      </c>
+      <c r="H161" s="11" t="s">
+        <v>839</v>
+      </c>
+      <c r="I161" s="8"/>
+      <c r="J161" s="8" t="s">
+        <v>388</v>
+      </c>
+      <c r="K161" s="11" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="162" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A162" s="9">
+        <v>61</v>
+      </c>
+      <c r="B162" s="8" t="s">
+        <v>847</v>
+      </c>
+      <c r="C162" s="8" t="s">
+        <v>921</v>
+      </c>
+      <c r="D162" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="E162" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="F162" s="4">
+        <v>1222106859</v>
+      </c>
+      <c r="G162" s="8" t="s">
+        <v>848</v>
+      </c>
+      <c r="H162" s="8" t="s">
+        <v>849</v>
+      </c>
+      <c r="I162" s="8"/>
+      <c r="J162" s="8" t="s">
+        <v>929</v>
+      </c>
+      <c r="K162" s="8" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="163" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A163" s="9">
+        <v>62</v>
+      </c>
+      <c r="B163" s="8" t="s">
+        <v>851</v>
+      </c>
+      <c r="C163" s="8" t="s">
+        <v>852</v>
+      </c>
+      <c r="D163" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="E163" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="F163" s="4">
+        <v>1005708619</v>
+      </c>
+      <c r="G163" s="8" t="s">
+        <v>853</v>
+      </c>
+      <c r="H163" s="8" t="s">
+        <v>854</v>
+      </c>
+      <c r="I163" s="8"/>
+      <c r="J163" s="8" t="s">
+        <v>387</v>
+      </c>
+      <c r="K163" s="8" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="164" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A164" s="9">
+        <v>63</v>
+      </c>
+      <c r="B164" s="8" t="s">
+        <v>856</v>
+      </c>
+      <c r="C164" s="8" t="s">
+        <v>857</v>
+      </c>
+      <c r="D164" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="E164" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F164" s="4">
+        <v>122210685932</v>
+      </c>
+      <c r="G164" s="8" t="s">
+        <v>858</v>
+      </c>
+      <c r="H164" s="8" t="s">
+        <v>859</v>
+      </c>
+      <c r="I164" s="8"/>
+      <c r="J164" s="8" t="s">
+        <v>388</v>
+      </c>
+      <c r="K164" s="8" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="165" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A165" s="9">
+        <v>64</v>
+      </c>
+      <c r="B165" s="8" t="s">
+        <v>861</v>
+      </c>
+      <c r="C165" s="8" t="s">
+        <v>862</v>
+      </c>
+      <c r="D165" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="E165" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="F165" s="4">
+        <v>101111220</v>
+      </c>
+      <c r="G165" s="8" t="s">
+        <v>863</v>
+      </c>
+      <c r="H165" s="8" t="s">
+        <v>864</v>
+      </c>
+      <c r="I165" s="8"/>
+      <c r="J165" s="8" t="s">
+        <v>389</v>
+      </c>
+      <c r="K165" s="8" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="166" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A166" s="9">
+        <v>65</v>
+      </c>
+      <c r="B166" s="8" t="s">
+        <v>865</v>
+      </c>
+      <c r="C166" s="8" t="s">
+        <v>866</v>
+      </c>
+      <c r="D166" s="8" t="s">
+        <v>867</v>
+      </c>
+      <c r="E166" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F166" s="4">
+        <v>1001111220</v>
+      </c>
+      <c r="G166" s="8" t="s">
+        <v>868</v>
+      </c>
+      <c r="H166" s="8" t="s">
+        <v>869</v>
+      </c>
+      <c r="I166" s="8"/>
+      <c r="J166" s="8" t="s">
+        <v>392</v>
+      </c>
+      <c r="K166" s="8" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="167" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A167" s="9">
+        <v>66</v>
+      </c>
+      <c r="B167" s="8" t="s">
+        <v>870</v>
+      </c>
+      <c r="C167" s="8" t="s">
+        <v>871</v>
+      </c>
+      <c r="D167" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="E167" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="F167" s="4">
+        <v>1001111220</v>
+      </c>
+      <c r="G167" s="8" t="s">
+        <v>872</v>
+      </c>
+      <c r="H167" s="8" t="s">
+        <v>873</v>
+      </c>
+      <c r="I167" s="8"/>
+      <c r="J167" s="8" t="s">
+        <v>390</v>
+      </c>
+      <c r="K167" s="8" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="168" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A168" s="9">
+        <v>67</v>
+      </c>
+      <c r="B168" s="8" t="s">
+        <v>874</v>
+      </c>
+      <c r="C168" s="8" t="s">
+        <v>875</v>
+      </c>
+      <c r="D168" s="8" t="s">
+        <v>867</v>
+      </c>
+      <c r="E168" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F168" s="4">
+        <v>1005287722</v>
+      </c>
+      <c r="G168" s="8" t="s">
+        <v>876</v>
+      </c>
+      <c r="H168" s="8" t="s">
+        <v>877</v>
+      </c>
+      <c r="I168" s="8"/>
+      <c r="J168" s="8" t="s">
+        <v>387</v>
+      </c>
+      <c r="K168" s="8" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="169" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A169" s="9">
+        <v>68</v>
+      </c>
+      <c r="B169" s="8" t="s">
+        <v>878</v>
+      </c>
+      <c r="C169" s="8" t="s">
+        <v>922</v>
+      </c>
+      <c r="D169" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="E169" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="F169" s="4">
+        <v>1020900908</v>
+      </c>
+      <c r="G169" s="8" t="s">
+        <v>879</v>
+      </c>
+      <c r="H169" s="8" t="s">
+        <v>880</v>
+      </c>
+      <c r="I169" s="8"/>
+      <c r="J169" s="8" t="s">
+        <v>388</v>
+      </c>
+      <c r="K169" s="8" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="170" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A170" s="9">
+        <v>69</v>
+      </c>
+      <c r="B170" s="8" t="s">
+        <v>881</v>
+      </c>
+      <c r="C170" s="8" t="s">
+        <v>882</v>
+      </c>
+      <c r="D170" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="E170" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F170" s="4">
+        <v>1212315094</v>
+      </c>
+      <c r="G170" s="8" t="s">
+        <v>883</v>
+      </c>
+      <c r="H170" s="8" t="s">
+        <v>884</v>
+      </c>
+      <c r="I170" s="8"/>
+      <c r="J170" s="8" t="s">
+        <v>389</v>
+      </c>
+      <c r="K170" s="8" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="171" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A171" s="9">
+        <v>70</v>
+      </c>
+      <c r="B171" s="8" t="s">
+        <v>885</v>
+      </c>
+      <c r="C171" s="8" t="s">
+        <v>886</v>
+      </c>
+      <c r="D171" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="E171" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F171" s="4">
+        <v>34628098</v>
+      </c>
+      <c r="G171" s="8" t="s">
+        <v>887</v>
+      </c>
+      <c r="H171" s="8" t="s">
+        <v>888</v>
+      </c>
+      <c r="I171" s="8"/>
+      <c r="J171" s="8" t="s">
+        <v>392</v>
+      </c>
+      <c r="K171" s="8" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="172" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A172" s="9">
+        <v>71</v>
+      </c>
+      <c r="B172" s="8" t="s">
+        <v>889</v>
+      </c>
+      <c r="C172" s="8" t="s">
+        <v>890</v>
+      </c>
+      <c r="D172" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="E172" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F172" s="4">
+        <v>1008809166</v>
+      </c>
+      <c r="G172" s="8" t="s">
+        <v>891</v>
+      </c>
+      <c r="H172" s="8" t="s">
+        <v>892</v>
+      </c>
+      <c r="I172" s="8"/>
+      <c r="J172" s="8" t="s">
+        <v>390</v>
+      </c>
+      <c r="K172" s="8" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="173" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A173" s="9">
+        <v>72</v>
+      </c>
+      <c r="B173" s="8" t="s">
+        <v>893</v>
+      </c>
+      <c r="C173" s="8" t="s">
+        <v>894</v>
+      </c>
+      <c r="D173" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="E173" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F173" s="4">
+        <v>1001121625</v>
+      </c>
+      <c r="G173" s="8" t="s">
+        <v>895</v>
+      </c>
+      <c r="H173" s="8" t="s">
+        <v>896</v>
+      </c>
+      <c r="I173" s="8"/>
+      <c r="J173" s="8" t="s">
+        <v>387</v>
+      </c>
+      <c r="K173" s="8" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="174" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A174" s="9">
+        <v>73</v>
+      </c>
+      <c r="B174" s="8" t="s">
+        <v>897</v>
+      </c>
+      <c r="C174" s="8" t="s">
+        <v>923</v>
+      </c>
+      <c r="D174" s="8" t="s">
+        <v>927</v>
+      </c>
+      <c r="E174" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F174" s="4">
+        <v>12018470746</v>
+      </c>
+      <c r="G174" s="8" t="s">
+        <v>898</v>
+      </c>
+      <c r="H174" s="8" t="s">
+        <v>899</v>
+      </c>
+      <c r="I174" s="8"/>
+      <c r="J174" s="8" t="s">
+        <v>388</v>
+      </c>
+      <c r="K174" s="8" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="175" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A175" s="9">
+        <v>74</v>
+      </c>
+      <c r="B175" s="8" t="s">
+        <v>900</v>
+      </c>
+      <c r="C175" s="8" t="s">
+        <v>924</v>
+      </c>
+      <c r="D175" s="8" t="s">
+        <v>928</v>
+      </c>
+      <c r="E175" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="F175" s="4">
+        <v>1091080020</v>
+      </c>
+      <c r="G175" s="8" t="s">
+        <v>901</v>
+      </c>
+      <c r="H175" s="8" t="s">
+        <v>902</v>
+      </c>
+      <c r="I175" s="8"/>
+      <c r="J175" s="8" t="s">
+        <v>389</v>
+      </c>
+      <c r="K175" s="8" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="176" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A176" s="9">
+        <v>75</v>
+      </c>
+      <c r="B176" s="8" t="s">
+        <v>903</v>
+      </c>
+      <c r="C176" s="8" t="s">
+        <v>925</v>
+      </c>
+      <c r="D176" s="8" t="s">
+        <v>928</v>
+      </c>
+      <c r="E176" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="F176" s="4">
+        <v>10020372047</v>
+      </c>
+      <c r="G176" s="8" t="s">
+        <v>904</v>
+      </c>
+      <c r="H176" s="8" t="s">
+        <v>905</v>
+      </c>
+      <c r="I176" s="8"/>
+      <c r="J176" s="8" t="s">
+        <v>392</v>
+      </c>
+      <c r="K176" s="8" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="177" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A177" s="9">
+        <v>76</v>
+      </c>
+      <c r="B177" s="8" t="s">
+        <v>906</v>
+      </c>
+      <c r="C177" s="8" t="s">
+        <v>907</v>
+      </c>
+      <c r="D177" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="E177" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F177" s="4">
+        <v>1001146603</v>
+      </c>
+      <c r="G177" s="8" t="s">
+        <v>908</v>
+      </c>
+      <c r="H177" s="8" t="s">
+        <v>909</v>
+      </c>
+      <c r="I177" s="8"/>
+      <c r="J177" s="8" t="s">
+        <v>390</v>
+      </c>
+      <c r="K177" s="8" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="178" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A178" s="9">
+        <v>77</v>
+      </c>
+      <c r="B178" s="8" t="s">
+        <v>910</v>
+      </c>
+      <c r="C178" s="8" t="s">
+        <v>926</v>
+      </c>
+      <c r="D178" s="8" t="s">
+        <v>928</v>
+      </c>
+      <c r="E178" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="F178" s="4">
+        <v>1224403717</v>
+      </c>
+      <c r="G178" s="8" t="s">
+        <v>911</v>
+      </c>
+      <c r="H178" s="8" t="s">
+        <v>912</v>
+      </c>
+      <c r="I178" s="8"/>
+      <c r="J178" s="8" t="s">
+        <v>387</v>
+      </c>
+      <c r="K178" s="8" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="179" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A179" s="9">
+        <v>78</v>
+      </c>
+      <c r="B179" s="8" t="s">
+        <v>913</v>
+      </c>
+      <c r="C179" s="8" t="s">
+        <v>914</v>
+      </c>
+      <c r="D179" s="8" t="s">
+        <v>611</v>
+      </c>
+      <c r="E179" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F179" s="4">
+        <v>33916220434</v>
+      </c>
+      <c r="G179" s="8" t="s">
+        <v>915</v>
+      </c>
+      <c r="H179" s="8" t="s">
+        <v>916</v>
+      </c>
+      <c r="I179" s="8"/>
+      <c r="J179" s="8" t="s">
+        <v>388</v>
+      </c>
+      <c r="K179" s="8" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="180" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A180" s="3">
+        <v>79</v>
+      </c>
+      <c r="B180" s="11" t="s">
+        <v>917</v>
+      </c>
+      <c r="C180" s="11" t="s">
+        <v>918</v>
+      </c>
+      <c r="D180" s="11" t="s">
+        <v>811</v>
+      </c>
+      <c r="E180" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F180" s="23">
+        <v>502201126</v>
+      </c>
+      <c r="G180" s="11" t="s">
+        <v>919</v>
+      </c>
+      <c r="H180" s="11" t="s">
+        <v>920</v>
+      </c>
+      <c r="I180" s="8"/>
+      <c r="J180" s="8" t="s">
+        <v>389</v>
+      </c>
+      <c r="K180" s="11" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="181" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A181" s="3">
+        <v>80</v>
+      </c>
+      <c r="B181" s="11" t="s">
+        <v>930</v>
+      </c>
+      <c r="C181" s="11" t="s">
+        <v>931</v>
+      </c>
+      <c r="D181" s="11" t="s">
+        <v>932</v>
+      </c>
+      <c r="E181" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F181" s="23">
+        <v>502201128</v>
+      </c>
+      <c r="G181" s="11" t="s">
+        <v>933</v>
+      </c>
+      <c r="H181" s="11" t="s">
+        <v>934</v>
+      </c>
+      <c r="I181" s="8"/>
+      <c r="J181" s="8" t="s">
+        <v>392</v>
+      </c>
+      <c r="K181" s="11" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="182" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A182" s="9">
+        <v>81</v>
+      </c>
+      <c r="B182" s="8" t="s">
+        <v>935</v>
+      </c>
+      <c r="C182" s="8" t="s">
+        <v>936</v>
+      </c>
+      <c r="D182" s="8" t="s">
+        <v>937</v>
+      </c>
+      <c r="E182" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F182" s="4">
+        <v>22618087</v>
+      </c>
+      <c r="G182" s="8" t="s">
+        <v>938</v>
+      </c>
+      <c r="H182" s="8" t="s">
+        <v>939</v>
+      </c>
+      <c r="I182" s="8"/>
+      <c r="J182" s="8" t="s">
+        <v>390</v>
+      </c>
+      <c r="K182" s="8" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="183" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A183" s="9">
+        <v>82</v>
+      </c>
+      <c r="B183" s="8" t="s">
+        <v>941</v>
+      </c>
+      <c r="C183" s="8" t="s">
+        <v>942</v>
+      </c>
+      <c r="D183" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="E183" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F183" s="4">
+        <v>32201130</v>
+      </c>
+      <c r="G183" s="8" t="s">
+        <v>943</v>
+      </c>
+      <c r="H183" s="8" t="s">
+        <v>944</v>
+      </c>
+      <c r="I183" s="8"/>
+      <c r="J183" s="8" t="s">
+        <v>387</v>
+      </c>
+      <c r="K183" s="8" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="184" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A184" s="9">
+        <v>83</v>
+      </c>
+      <c r="B184" s="8" t="s">
+        <v>946</v>
+      </c>
+      <c r="C184" s="8" t="s">
+        <v>947</v>
+      </c>
+      <c r="D184" s="8" t="s">
+        <v>948</v>
+      </c>
+      <c r="E184" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F184" s="4">
+        <v>9615541</v>
+      </c>
+      <c r="G184" s="8" t="s">
+        <v>949</v>
+      </c>
+      <c r="H184" s="8" t="s">
+        <v>950</v>
+      </c>
+      <c r="I184" s="8"/>
+      <c r="J184" s="8" t="s">
+        <v>388</v>
+      </c>
+      <c r="K184" s="8" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="185" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A185" s="9">
+        <v>84</v>
+      </c>
+      <c r="B185" s="8" t="s">
+        <v>952</v>
+      </c>
+      <c r="C185" s="8" t="s">
+        <v>953</v>
+      </c>
+      <c r="D185" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="E185" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F185" s="4">
+        <v>34591146</v>
+      </c>
+      <c r="G185" s="8" t="s">
+        <v>954</v>
+      </c>
+      <c r="H185" s="8" t="s">
+        <v>955</v>
+      </c>
+      <c r="I185" s="8"/>
+      <c r="J185" s="8" t="s">
+        <v>389</v>
+      </c>
+      <c r="K185" s="8" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="186" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A186" s="9">
+        <v>85</v>
+      </c>
+      <c r="B186" s="8" t="s">
+        <v>957</v>
+      </c>
+      <c r="C186" s="8" t="s">
+        <v>958</v>
+      </c>
+      <c r="D186" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="E186" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F186" s="4">
+        <v>34591148</v>
+      </c>
+      <c r="G186" s="8" t="s">
+        <v>959</v>
+      </c>
+      <c r="H186" s="8" t="s">
+        <v>960</v>
+      </c>
+      <c r="I186" s="8"/>
+      <c r="J186" s="8" t="s">
+        <v>392</v>
+      </c>
+      <c r="K186" s="8" t="s">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="187" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A187" s="9">
+        <v>86</v>
+      </c>
+      <c r="B187" s="8" t="s">
+        <v>962</v>
+      </c>
+      <c r="C187" s="8" t="s">
+        <v>963</v>
+      </c>
+      <c r="D187" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="E187" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F187" s="4">
+        <v>32201132</v>
+      </c>
+      <c r="G187" s="8" t="s">
+        <v>964</v>
+      </c>
+      <c r="H187" s="8" t="s">
+        <v>965</v>
+      </c>
+      <c r="I187" s="8"/>
+      <c r="J187" s="8" t="s">
+        <v>390</v>
+      </c>
+      <c r="K187" s="8" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="188" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A188" s="9">
+        <v>87</v>
+      </c>
+      <c r="B188" s="8" t="s">
+        <v>966</v>
+      </c>
+      <c r="C188" s="8" t="s">
+        <v>967</v>
+      </c>
+      <c r="D188" s="8" t="s">
+        <v>968</v>
+      </c>
+      <c r="E188" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F188" s="4">
+        <v>9793451</v>
+      </c>
+      <c r="G188" s="8" t="s">
+        <v>969</v>
+      </c>
+      <c r="H188" s="8" t="s">
+        <v>970</v>
+      </c>
+      <c r="I188" s="8"/>
+      <c r="J188" s="8" t="s">
+        <v>387</v>
+      </c>
+      <c r="K188" s="8" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="189" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A189" s="9">
+        <v>88</v>
+      </c>
+      <c r="B189" s="8" t="s">
+        <v>971</v>
+      </c>
+      <c r="C189" s="8" t="s">
+        <v>972</v>
+      </c>
+      <c r="D189" s="8" t="s">
+        <v>973</v>
+      </c>
+      <c r="E189" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F189" s="4">
+        <v>224034062</v>
+      </c>
+      <c r="G189" s="8" t="s">
+        <v>974</v>
+      </c>
+      <c r="H189" s="8" t="s">
+        <v>975</v>
+      </c>
+      <c r="I189" s="8"/>
+      <c r="J189" s="8" t="s">
+        <v>388</v>
+      </c>
+      <c r="K189" s="8" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="190" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A190" s="9">
+        <v>89</v>
+      </c>
+      <c r="B190" s="8" t="s">
+        <v>976</v>
+      </c>
+      <c r="C190" s="8" t="s">
+        <v>977</v>
+      </c>
+      <c r="D190" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E190" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F190" s="4">
+        <v>237602396</v>
+      </c>
+      <c r="G190" s="8" t="s">
+        <v>978</v>
+      </c>
+      <c r="H190" s="8" t="s">
+        <v>979</v>
+      </c>
+      <c r="I190" s="8"/>
+      <c r="J190" s="8" t="s">
+        <v>389</v>
+      </c>
+      <c r="K190" s="8" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="191" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A191" s="9">
+        <v>90</v>
+      </c>
+      <c r="B191" s="8" t="s">
+        <v>980</v>
+      </c>
+      <c r="C191" s="8" t="s">
+        <v>981</v>
+      </c>
+      <c r="D191" s="8" t="s">
+        <v>982</v>
+      </c>
+      <c r="E191" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F191" s="4">
+        <v>235391677</v>
+      </c>
+      <c r="G191" s="8" t="s">
+        <v>983</v>
+      </c>
+      <c r="H191" s="8" t="s">
+        <v>984</v>
+      </c>
+      <c r="I191" s="8"/>
+      <c r="J191" s="8" t="s">
+        <v>392</v>
+      </c>
+      <c r="K191" s="8" t="s">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="192" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A192" s="9">
+        <v>91</v>
+      </c>
+      <c r="B192" s="8" t="s">
+        <v>985</v>
+      </c>
+      <c r="C192" s="8" t="s">
+        <v>986</v>
+      </c>
+      <c r="D192" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="E192" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F192" s="4">
+        <v>34591150</v>
+      </c>
+      <c r="G192" s="8" t="s">
+        <v>987</v>
+      </c>
+      <c r="H192" s="8" t="s">
+        <v>988</v>
+      </c>
+      <c r="I192" s="8"/>
+      <c r="J192" s="8" t="s">
+        <v>390</v>
+      </c>
+      <c r="K192" s="8" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="193" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A193" s="9">
+        <v>92</v>
+      </c>
+      <c r="B193" s="8" t="s">
+        <v>989</v>
+      </c>
+      <c r="C193" s="8" t="s">
+        <v>990</v>
+      </c>
+      <c r="D193" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="E193" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F193" s="4">
+        <v>34591152</v>
+      </c>
+      <c r="G193" s="8" t="s">
+        <v>991</v>
+      </c>
+      <c r="H193" s="8" t="s">
+        <v>992</v>
+      </c>
+      <c r="I193" s="8"/>
+      <c r="J193" s="8" t="s">
+        <v>387</v>
+      </c>
+      <c r="K193" s="8" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="194" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A194" s="9">
+        <v>93</v>
+      </c>
+      <c r="B194" s="8" t="s">
+        <v>993</v>
+      </c>
+      <c r="C194" s="8" t="s">
+        <v>994</v>
+      </c>
+      <c r="D194" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="E194" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F194" s="4">
+        <v>34591154</v>
+      </c>
+      <c r="G194" s="8" t="s">
+        <v>995</v>
+      </c>
+      <c r="H194" s="8" t="s">
+        <v>996</v>
+      </c>
+      <c r="I194" s="8"/>
+      <c r="J194" s="8" t="s">
+        <v>388</v>
+      </c>
+      <c r="K194" s="8" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="195" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A195" s="9">
+        <v>94</v>
+      </c>
+      <c r="B195" s="8" t="s">
+        <v>997</v>
+      </c>
+      <c r="C195" s="8" t="s">
+        <v>998</v>
+      </c>
+      <c r="D195" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="E195" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F195" s="4">
+        <v>34591156</v>
+      </c>
+      <c r="G195" s="8" t="s">
+        <v>999</v>
+      </c>
+      <c r="H195" s="8" t="s">
+        <v>1000</v>
+      </c>
+      <c r="I195" s="8"/>
+      <c r="J195" s="8" t="s">
+        <v>389</v>
+      </c>
+      <c r="K195" s="8" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="196" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A196" s="9">
+        <v>95</v>
+      </c>
+      <c r="B196" s="8" t="s">
+        <v>1001</v>
+      </c>
+      <c r="C196" s="8" t="s">
+        <v>1002</v>
+      </c>
+      <c r="D196" s="8" t="s">
+        <v>1003</v>
+      </c>
+      <c r="E196" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F196" s="4">
+        <v>227166718</v>
+      </c>
+      <c r="G196" s="8" t="s">
+        <v>1004</v>
+      </c>
+      <c r="H196" s="8" t="s">
+        <v>1005</v>
+      </c>
+      <c r="I196" s="8"/>
+      <c r="J196" s="8" t="s">
+        <v>392</v>
+      </c>
+      <c r="K196" s="8" t="s">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="197" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A197" s="9">
+        <v>96</v>
+      </c>
+      <c r="B197" s="8" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C197" s="8" t="s">
+        <v>1007</v>
+      </c>
+      <c r="D197" s="8" t="s">
+        <v>1008</v>
+      </c>
+      <c r="E197" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F197" s="4">
+        <v>225257097</v>
+      </c>
+      <c r="G197" s="8" t="s">
+        <v>1009</v>
+      </c>
+      <c r="H197" s="8" t="s">
+        <v>1010</v>
+      </c>
+      <c r="I197" s="8"/>
+      <c r="J197" s="8" t="s">
+        <v>390</v>
+      </c>
+      <c r="K197" s="8" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="198" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A198" s="9">
+        <v>97</v>
+      </c>
+      <c r="B198" s="8" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C198" s="8" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D198" s="8" t="s">
+        <v>1013</v>
+      </c>
+      <c r="E198" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F198" s="4">
+        <v>23350187</v>
+      </c>
+      <c r="G198" s="8" t="s">
+        <v>1014</v>
+      </c>
+      <c r="H198" s="8" t="s">
+        <v>1015</v>
+      </c>
+      <c r="I198" s="8"/>
+      <c r="J198" s="8" t="s">
+        <v>387</v>
+      </c>
+      <c r="K198" s="8" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="199" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A199" s="9">
+        <v>98</v>
+      </c>
+      <c r="B199" s="8" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C199" s="8" t="s">
+        <v>1017</v>
+      </c>
+      <c r="D199" s="8" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E199" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F199" s="4">
+        <v>225758597</v>
+      </c>
+      <c r="G199" s="8" t="s">
+        <v>1019</v>
+      </c>
+      <c r="H199" s="8" t="s">
+        <v>1020</v>
+      </c>
+      <c r="I199" s="8"/>
+      <c r="J199" s="8" t="s">
+        <v>388</v>
+      </c>
+      <c r="K199" s="8" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="200" spans="1:11" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A200" s="9">
+        <v>99</v>
+      </c>
+      <c r="B200" s="8" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C200" s="8" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D200" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="E200" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F200" s="4">
+        <v>28364190</v>
+      </c>
+      <c r="G200" s="8" t="s">
+        <v>1023</v>
+      </c>
+      <c r="H200" s="8" t="s">
+        <v>1024</v>
+      </c>
+      <c r="I200" s="8"/>
+      <c r="J200" s="8" t="s">
+        <v>389</v>
+      </c>
+      <c r="K200" s="8" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="201" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A201" s="3">
+        <v>100</v>
+      </c>
+      <c r="B201" s="11" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C201" s="11" t="s">
+        <v>1028</v>
+      </c>
+      <c r="D201" s="11" t="s">
+        <v>1029</v>
+      </c>
+      <c r="E201" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F201" s="23">
+        <v>34591158</v>
+      </c>
+      <c r="G201" s="11" t="s">
+        <v>1026</v>
+      </c>
+      <c r="H201" s="11" t="s">
+        <v>1027</v>
+      </c>
+      <c r="I201" s="11"/>
+      <c r="J201" s="11" t="s">
+        <v>392</v>
+      </c>
+      <c r="K201" s="11" t="s">
+        <v>961</v>
       </c>
     </row>
   </sheetData>
